--- a/josh_auditoria_manual_2025.xlsx
+++ b/josh_auditoria_manual_2025.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -140,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,9 +157,9 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -172,6 +171,8 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -724,7 +725,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="21" t="n">
         <v>45658</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -754,7 +755,7 @@
       <c r="N7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="22" t="n">
         <v>45659</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -784,7 +785,7 @@
       <c r="N8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="22" t="n">
         <v>45660</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -824,7 +825,7 @@
       <c r="N9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="22" t="n">
         <v>45663</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -874,7 +875,7 @@
       <c r="N10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="22" t="n">
         <v>45664</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -924,7 +925,7 @@
       <c r="N11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="22" t="n">
         <v>45665</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -964,7 +965,7 @@
       <c r="N12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="22" t="n">
         <v>45666</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -1014,7 +1015,7 @@
       <c r="N13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="22" t="n">
         <v>45667</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -1064,7 +1065,7 @@
       <c r="N14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="22" t="n">
         <v>45670</v>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -1104,7 +1105,7 @@
       <c r="N15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="22" t="n">
         <v>45671</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -1134,7 +1135,7 @@
       <c r="N16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n">
+      <c r="A17" s="22" t="n">
         <v>45672</v>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -1184,7 +1185,7 @@
       <c r="N17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="22" t="n">
         <v>45673</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -1234,7 +1235,7 @@
       <c r="N18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="n">
+      <c r="A19" s="22" t="n">
         <v>45674</v>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1284,7 +1285,7 @@
       <c r="N19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n">
+      <c r="A20" s="22" t="n">
         <v>45677</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -1324,7 +1325,7 @@
       <c r="N20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="22" t="n">
         <v>45678</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -1374,7 +1375,7 @@
       <c r="N21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n">
+      <c r="A22" s="22" t="n">
         <v>45679</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -1414,7 +1415,7 @@
       <c r="N22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="22" t="n">
         <v>45680</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1464,7 +1465,7 @@
       <c r="N23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n">
+      <c r="A24" s="22" t="n">
         <v>45681</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -1504,7 +1505,7 @@
       <c r="N24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="22" t="n">
         <v>45684</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -1554,7 +1555,7 @@
       <c r="N25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="n">
+      <c r="A26" s="22" t="n">
         <v>45685</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -1594,7 +1595,7 @@
       <c r="N26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="22" t="n">
         <v>45686</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -1644,7 +1645,7 @@
       <c r="N27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n">
+      <c r="A28" s="22" t="n">
         <v>45687</v>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -1694,7 +1695,7 @@
       <c r="N28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="22" t="n">
         <v>45688</v>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1744,7 +1745,7 @@
       <c r="N29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="22" t="n">
         <v>45691</v>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -1784,7 +1785,7 @@
       <c r="N30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="22" t="n">
         <v>45692</v>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -1834,7 +1835,7 @@
       <c r="N31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n">
+      <c r="A32" s="22" t="n">
         <v>45693</v>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -1874,7 +1875,7 @@
       <c r="N32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n">
+      <c r="A33" s="22" t="n">
         <v>45694</v>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1914,7 +1915,7 @@
       <c r="N33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n">
+      <c r="A34" s="22" t="n">
         <v>45695</v>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -1964,7 +1965,7 @@
       <c r="N34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n">
+      <c r="A35" s="22" t="n">
         <v>45698</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -2014,7 +2015,7 @@
       <c r="N35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n">
+      <c r="A36" s="22" t="n">
         <v>45699</v>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -2054,7 +2055,7 @@
       <c r="N36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n">
+      <c r="A37" s="22" t="n">
         <v>45700</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -2094,7 +2095,7 @@
       <c r="N37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n">
+      <c r="A38" s="22" t="n">
         <v>45701</v>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -2144,7 +2145,7 @@
       <c r="N38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n">
+      <c r="A39" s="22" t="n">
         <v>45702</v>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -2184,7 +2185,7 @@
       <c r="N39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n">
+      <c r="A40" s="22" t="n">
         <v>45705</v>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -2234,7 +2235,7 @@
       <c r="N40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n">
+      <c r="A41" s="22" t="n">
         <v>45706</v>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -2274,7 +2275,7 @@
       <c r="N41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n">
+      <c r="A42" s="22" t="n">
         <v>45707</v>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -2324,7 +2325,7 @@
       <c r="N42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n">
+      <c r="A43" s="22" t="n">
         <v>45708</v>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -2364,7 +2365,7 @@
       <c r="N43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="n">
+      <c r="A44" s="22" t="n">
         <v>45709</v>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -2404,7 +2405,7 @@
       <c r="N44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="n">
+      <c r="A45" s="22" t="n">
         <v>45712</v>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -2444,7 +2445,7 @@
       <c r="N45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n">
+      <c r="A46" s="22" t="n">
         <v>45713</v>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -2484,7 +2485,7 @@
       <c r="N46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n">
+      <c r="A47" s="22" t="n">
         <v>45714</v>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -2524,7 +2525,7 @@
       <c r="N47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="n">
+      <c r="A48" s="22" t="n">
         <v>45715</v>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -2564,7 +2565,7 @@
       <c r="N48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="n">
+      <c r="A49" s="22" t="n">
         <v>45716</v>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -2614,7 +2615,7 @@
       <c r="N49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n">
+      <c r="A50" s="22" t="n">
         <v>45719</v>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -2664,7 +2665,7 @@
       <c r="N50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="22" t="n">
         <v>45720</v>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -2714,7 +2715,7 @@
       <c r="N51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="22" t="n">
         <v>45721</v>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -2764,7 +2765,7 @@
       <c r="N52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="22" t="n">
         <v>45722</v>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -2814,7 +2815,7 @@
       <c r="N53" s="17" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n">
+      <c r="A54" s="22" t="n">
         <v>45723</v>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -2864,7 +2865,7 @@
       <c r="N54" s="17" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n">
+      <c r="A55" s="22" t="n">
         <v>45726</v>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -2914,7 +2915,7 @@
       <c r="N55" s="17" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="n">
+      <c r="A56" s="22" t="n">
         <v>45727</v>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -2964,7 +2965,7 @@
       <c r="N56" s="17" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="n">
+      <c r="A57" s="22" t="n">
         <v>45728</v>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -3014,7 +3015,7 @@
       <c r="N57" s="17" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="n">
+      <c r="A58" s="22" t="n">
         <v>45729</v>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -3064,7 +3065,7 @@
       <c r="N58" s="17" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="n">
+      <c r="A59" s="22" t="n">
         <v>45730</v>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -3114,7 +3115,7 @@
       <c r="N59" s="17" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="n">
+      <c r="A60" s="22" t="n">
         <v>45733</v>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -3164,7 +3165,7 @@
       <c r="N60" s="17" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="n">
+      <c r="A61" s="22" t="n">
         <v>45734</v>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -3204,7 +3205,7 @@
       <c r="N61" s="17" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n">
+      <c r="A62" s="22" t="n">
         <v>45735</v>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -3254,7 +3255,7 @@
       <c r="N62" s="17" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="n">
+      <c r="A63" s="22" t="n">
         <v>45736</v>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -3294,7 +3295,7 @@
       <c r="N63" s="17" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n">
+      <c r="A64" s="22" t="n">
         <v>45737</v>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -3344,7 +3345,7 @@
       <c r="N64" s="17" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n">
+      <c r="A65" s="22" t="n">
         <v>45740</v>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -3394,7 +3395,7 @@
       <c r="N65" s="17" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="n">
+      <c r="A66" s="22" t="n">
         <v>45741</v>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -3444,7 +3445,7 @@
       <c r="N66" s="17" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="n">
+      <c r="A67" s="22" t="n">
         <v>45742</v>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -3494,7 +3495,7 @@
       <c r="N67" s="17" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="n">
+      <c r="A68" s="22" t="n">
         <v>45743</v>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -3524,7 +3525,7 @@
       <c r="N68" s="17" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="n">
+      <c r="A69" s="22" t="n">
         <v>45744</v>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -3574,7 +3575,7 @@
       <c r="N69" s="17" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="n">
+      <c r="A70" s="22" t="n">
         <v>45747</v>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -3624,7 +3625,7 @@
       <c r="N70" s="17" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="n">
+      <c r="A71" s="22" t="n">
         <v>45748</v>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -3664,7 +3665,7 @@
       <c r="N71" s="17" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="n">
+      <c r="A72" s="22" t="n">
         <v>45749</v>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -3714,7 +3715,7 @@
       <c r="N72" s="17" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="n">
+      <c r="A73" s="22" t="n">
         <v>45750</v>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -3754,7 +3755,7 @@
       <c r="N73" s="17" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="n">
+      <c r="A74" s="22" t="n">
         <v>45751</v>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -3804,7 +3805,7 @@
       <c r="N74" s="17" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="n">
+      <c r="A75" s="22" t="n">
         <v>45754</v>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -3854,7 +3855,7 @@
       <c r="N75" s="17" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="n">
+      <c r="A76" s="22" t="n">
         <v>45755</v>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -3904,7 +3905,7 @@
       <c r="N76" s="17" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="n">
+      <c r="A77" s="22" t="n">
         <v>45756</v>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -3954,7 +3955,7 @@
       <c r="N77" s="17" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="13" t="n">
+      <c r="A78" s="22" t="n">
         <v>45757</v>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -3994,7 +3995,7 @@
       <c r="N78" s="17" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="13" t="n">
+      <c r="A79" s="22" t="n">
         <v>45758</v>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -4034,7 +4035,7 @@
       <c r="N79" s="17" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="13" t="n">
+      <c r="A80" s="22" t="n">
         <v>45761</v>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -4084,7 +4085,7 @@
       <c r="N80" s="17" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="13" t="n">
+      <c r="A81" s="22" t="n">
         <v>45762</v>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -4134,7 +4135,7 @@
       <c r="N81" s="17" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="13" t="n">
+      <c r="A82" s="22" t="n">
         <v>45763</v>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -4184,7 +4185,7 @@
       <c r="N82" s="17" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="13" t="n">
+      <c r="A83" s="22" t="n">
         <v>45764</v>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -4234,7 +4235,7 @@
       <c r="N83" s="17" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="13" t="n">
+      <c r="A84" s="22" t="n">
         <v>45765</v>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -4284,7 +4285,7 @@
       <c r="N84" s="17" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="n">
+      <c r="A85" s="22" t="n">
         <v>45768</v>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -4334,7 +4335,7 @@
       <c r="N85" s="17" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="13" t="n">
+      <c r="A86" s="22" t="n">
         <v>45769</v>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -4374,7 +4375,7 @@
       <c r="N86" s="17" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="13" t="n">
+      <c r="A87" s="22" t="n">
         <v>45770</v>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -4414,7 +4415,7 @@
       <c r="N87" s="17" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="13" t="n">
+      <c r="A88" s="22" t="n">
         <v>45771</v>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -4454,7 +4455,7 @@
       <c r="N88" s="17" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="13" t="n">
+      <c r="A89" s="22" t="n">
         <v>45772</v>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -4504,7 +4505,7 @@
       <c r="N89" s="17" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="13" t="n">
+      <c r="A90" s="22" t="n">
         <v>45775</v>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -4554,7 +4555,7 @@
       <c r="N90" s="17" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="13" t="n">
+      <c r="A91" s="22" t="n">
         <v>45776</v>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -4604,7 +4605,7 @@
       <c r="N91" s="17" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="13" t="n">
+      <c r="A92" s="22" t="n">
         <v>45777</v>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -4634,7 +4635,7 @@
       <c r="N92" s="17" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="13" t="n">
+      <c r="A93" s="22" t="n">
         <v>45778</v>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -4684,7 +4685,7 @@
       <c r="N93" s="17" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="13" t="n">
+      <c r="A94" s="22" t="n">
         <v>45779</v>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -4734,7 +4735,7 @@
       <c r="N94" s="17" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="13" t="n">
+      <c r="A95" s="22" t="n">
         <v>45782</v>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -4784,7 +4785,7 @@
       <c r="N95" s="17" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="13" t="n">
+      <c r="A96" s="22" t="n">
         <v>45783</v>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -4834,7 +4835,7 @@
       <c r="N96" s="17" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="13" t="n">
+      <c r="A97" s="22" t="n">
         <v>45784</v>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -4864,7 +4865,7 @@
       <c r="N97" s="17" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="13" t="n">
+      <c r="A98" s="22" t="n">
         <v>45785</v>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -4914,7 +4915,7 @@
       <c r="N98" s="17" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="13" t="n">
+      <c r="A99" s="22" t="n">
         <v>45786</v>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -4964,7 +4965,7 @@
       <c r="N99" s="17" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="13" t="n">
+      <c r="A100" s="22" t="n">
         <v>45789</v>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -5004,7 +5005,7 @@
       <c r="N100" s="17" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="13" t="n">
+      <c r="A101" s="22" t="n">
         <v>45790</v>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -5054,7 +5055,7 @@
       <c r="N101" s="17" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="13" t="n">
+      <c r="A102" s="22" t="n">
         <v>45791</v>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -5104,7 +5105,7 @@
       <c r="N102" s="17" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="13" t="n">
+      <c r="A103" s="22" t="n">
         <v>45792</v>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -5144,7 +5145,7 @@
       <c r="N103" s="17" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="13" t="n">
+      <c r="A104" s="22" t="n">
         <v>45793</v>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -5194,7 +5195,7 @@
       <c r="N104" s="17" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="13" t="n">
+      <c r="A105" s="22" t="n">
         <v>45796</v>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -5234,7 +5235,7 @@
       <c r="N105" s="17" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="13" t="n">
+      <c r="A106" s="22" t="n">
         <v>45797</v>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -5284,7 +5285,7 @@
       <c r="N106" s="17" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="13" t="n">
+      <c r="A107" s="22" t="n">
         <v>45798</v>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -5324,7 +5325,7 @@
       <c r="N107" s="17" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="13" t="n">
+      <c r="A108" s="22" t="n">
         <v>45799</v>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -5374,7 +5375,7 @@
       <c r="N108" s="17" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="13" t="n">
+      <c r="A109" s="22" t="n">
         <v>45800</v>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -5424,7 +5425,7 @@
       <c r="N109" s="17" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="13" t="n">
+      <c r="A110" s="22" t="n">
         <v>45803</v>
       </c>
       <c r="B110" s="14" t="inlineStr">
@@ -5464,7 +5465,7 @@
       <c r="N110" s="17" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="13" t="n">
+      <c r="A111" s="22" t="n">
         <v>45804</v>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -5514,7 +5515,7 @@
       <c r="N111" s="17" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="13" t="n">
+      <c r="A112" s="22" t="n">
         <v>45805</v>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -5554,7 +5555,7 @@
       <c r="N112" s="17" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="13" t="n">
+      <c r="A113" s="22" t="n">
         <v>45806</v>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -5594,7 +5595,7 @@
       <c r="N113" s="17" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="13" t="n">
+      <c r="A114" s="22" t="n">
         <v>45807</v>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -5644,7 +5645,7 @@
       <c r="N114" s="17" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="13" t="n">
+      <c r="A115" s="22" t="n">
         <v>45810</v>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -5694,7 +5695,7 @@
       <c r="N115" s="17" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="13" t="n">
+      <c r="A116" s="22" t="n">
         <v>45811</v>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -5744,7 +5745,7 @@
       <c r="N116" s="17" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="13" t="n">
+      <c r="A117" s="22" t="n">
         <v>45812</v>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -5794,7 +5795,7 @@
       <c r="N117" s="17" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="13" t="n">
+      <c r="A118" s="22" t="n">
         <v>45813</v>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -5844,7 +5845,7 @@
       <c r="N118" s="17" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="13" t="n">
+      <c r="A119" s="22" t="n">
         <v>45814</v>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -5884,7 +5885,7 @@
       <c r="N119" s="17" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="13" t="n">
+      <c r="A120" s="22" t="n">
         <v>45817</v>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -5934,7 +5935,7 @@
       <c r="N120" s="17" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="13" t="n">
+      <c r="A121" s="22" t="n">
         <v>45818</v>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -5984,7 +5985,7 @@
       <c r="N121" s="17" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="13" t="n">
+      <c r="A122" s="22" t="n">
         <v>45819</v>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -6034,7 +6035,7 @@
       <c r="N122" s="17" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="13" t="n">
+      <c r="A123" s="22" t="n">
         <v>45820</v>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -6084,7 +6085,7 @@
       <c r="N123" s="17" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="13" t="n">
+      <c r="A124" s="22" t="n">
         <v>45821</v>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -6124,7 +6125,7 @@
       <c r="N124" s="17" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="13" t="n">
+      <c r="A125" s="22" t="n">
         <v>45824</v>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -6174,7 +6175,7 @@
       <c r="N125" s="17" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="13" t="n">
+      <c r="A126" s="22" t="n">
         <v>45825</v>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -6214,7 +6215,7 @@
       <c r="N126" s="17" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="13" t="n">
+      <c r="A127" s="22" t="n">
         <v>45826</v>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -6264,7 +6265,7 @@
       <c r="N127" s="17" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="13" t="n">
+      <c r="A128" s="22" t="n">
         <v>45827</v>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -6314,7 +6315,7 @@
       <c r="N128" s="17" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="13" t="n">
+      <c r="A129" s="22" t="n">
         <v>45828</v>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -6364,7 +6365,7 @@
       <c r="N129" s="17" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="13" t="n">
+      <c r="A130" s="22" t="n">
         <v>45831</v>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -6414,7 +6415,7 @@
       <c r="N130" s="17" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="13" t="n">
+      <c r="A131" s="22" t="n">
         <v>45832</v>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -6464,7 +6465,7 @@
       <c r="N131" s="17" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="13" t="n">
+      <c r="A132" s="22" t="n">
         <v>45833</v>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -6514,7 +6515,7 @@
       <c r="N132" s="17" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="13" t="n">
+      <c r="A133" s="22" t="n">
         <v>45834</v>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -6554,7 +6555,7 @@
       <c r="N133" s="17" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="13" t="n">
+      <c r="A134" s="22" t="n">
         <v>45835</v>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -6604,7 +6605,7 @@
       <c r="N134" s="17" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="13" t="n">
+      <c r="A135" s="22" t="n">
         <v>45838</v>
       </c>
       <c r="B135" s="14" t="inlineStr">
@@ -6654,7 +6655,7 @@
       <c r="N135" s="17" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="13" t="n">
+      <c r="A136" s="22" t="n">
         <v>45839</v>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -6704,7 +6705,7 @@
       <c r="N136" s="17" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="13" t="n">
+      <c r="A137" s="22" t="n">
         <v>45840</v>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -6744,7 +6745,7 @@
       <c r="N137" s="17" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="13" t="n">
+      <c r="A138" s="22" t="n">
         <v>45841</v>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -6784,7 +6785,7 @@
       <c r="N138" s="17" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="13" t="n">
+      <c r="A139" s="22" t="n">
         <v>45842</v>
       </c>
       <c r="B139" s="14" t="inlineStr">
@@ -6834,7 +6835,7 @@
       <c r="N139" s="17" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="13" t="n">
+      <c r="A140" s="22" t="n">
         <v>45845</v>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -6884,7 +6885,7 @@
       <c r="N140" s="17" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="13" t="n">
+      <c r="A141" s="22" t="n">
         <v>45846</v>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -6924,7 +6925,7 @@
       <c r="N141" s="17" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="13" t="n">
+      <c r="A142" s="22" t="n">
         <v>45847</v>
       </c>
       <c r="B142" s="14" t="inlineStr">
@@ -6964,7 +6965,7 @@
       <c r="N142" s="17" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="13" t="n">
+      <c r="A143" s="22" t="n">
         <v>45848</v>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -6994,7 +6995,7 @@
       <c r="N143" s="17" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="13" t="n">
+      <c r="A144" s="22" t="n">
         <v>45849</v>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -7034,7 +7035,7 @@
       <c r="N144" s="17" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="13" t="n">
+      <c r="A145" s="22" t="n">
         <v>45852</v>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -7064,7 +7065,7 @@
       <c r="N145" s="17" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="13" t="n">
+      <c r="A146" s="22" t="n">
         <v>45853</v>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -7114,7 +7115,7 @@
       <c r="N146" s="17" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="13" t="n">
+      <c r="A147" s="22" t="n">
         <v>45854</v>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -7164,7 +7165,7 @@
       <c r="N147" s="17" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="13" t="n">
+      <c r="A148" s="22" t="n">
         <v>45855</v>
       </c>
       <c r="B148" s="14" t="inlineStr">
@@ -7214,7 +7215,7 @@
       <c r="N148" s="17" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="13" t="n">
+      <c r="A149" s="22" t="n">
         <v>45856</v>
       </c>
       <c r="B149" s="14" t="inlineStr">
@@ -7254,7 +7255,7 @@
       <c r="N149" s="17" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="13" t="n">
+      <c r="A150" s="22" t="n">
         <v>45859</v>
       </c>
       <c r="B150" s="14" t="inlineStr">
@@ -7304,7 +7305,7 @@
       <c r="N150" s="17" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="13" t="n">
+      <c r="A151" s="22" t="n">
         <v>45860</v>
       </c>
       <c r="B151" s="14" t="inlineStr">
@@ -7354,7 +7355,7 @@
       <c r="N151" s="17" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="13" t="n">
+      <c r="A152" s="22" t="n">
         <v>45861</v>
       </c>
       <c r="B152" s="14" t="inlineStr">
@@ -7404,7 +7405,7 @@
       <c r="N152" s="17" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="13" t="n">
+      <c r="A153" s="22" t="n">
         <v>45862</v>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -7454,7 +7455,7 @@
       <c r="N153" s="17" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="13" t="n">
+      <c r="A154" s="22" t="n">
         <v>45863</v>
       </c>
       <c r="B154" s="14" t="inlineStr">
@@ -7504,7 +7505,7 @@
       <c r="N154" s="17" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="13" t="n">
+      <c r="A155" s="22" t="n">
         <v>45866</v>
       </c>
       <c r="B155" s="14" t="inlineStr">
@@ -7544,7 +7545,7 @@
       <c r="N155" s="17" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="13" t="n">
+      <c r="A156" s="22" t="n">
         <v>45867</v>
       </c>
       <c r="B156" s="14" t="inlineStr">
@@ -7594,7 +7595,7 @@
       <c r="N156" s="17" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="13" t="n">
+      <c r="A157" s="22" t="n">
         <v>45868</v>
       </c>
       <c r="B157" s="14" t="inlineStr">
@@ -7634,7 +7635,7 @@
       <c r="N157" s="17" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="13" t="n">
+      <c r="A158" s="22" t="n">
         <v>45869</v>
       </c>
       <c r="B158" s="14" t="inlineStr">
@@ -7684,7 +7685,7 @@
       <c r="N158" s="17" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="13" t="n">
+      <c r="A159" s="22" t="n">
         <v>45870</v>
       </c>
       <c r="B159" s="14" t="inlineStr">
@@ -7734,7 +7735,7 @@
       <c r="N159" s="17" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="13" t="n">
+      <c r="A160" s="22" t="n">
         <v>45873</v>
       </c>
       <c r="B160" s="14" t="inlineStr">
@@ -7784,7 +7785,7 @@
       <c r="N160" s="17" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="13" t="n">
+      <c r="A161" s="22" t="n">
         <v>45874</v>
       </c>
       <c r="B161" s="14" t="inlineStr">
@@ -7824,7 +7825,7 @@
       <c r="N161" s="17" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="13" t="n">
+      <c r="A162" s="22" t="n">
         <v>45875</v>
       </c>
       <c r="B162" s="14" t="inlineStr">
@@ -7854,7 +7855,7 @@
       <c r="N162" s="17" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="13" t="n">
+      <c r="A163" s="22" t="n">
         <v>45876</v>
       </c>
       <c r="B163" s="14" t="inlineStr">
@@ -7894,7 +7895,7 @@
       <c r="N163" s="17" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="13" t="n">
+      <c r="A164" s="22" t="n">
         <v>45877</v>
       </c>
       <c r="B164" s="14" t="inlineStr">
@@ -7934,7 +7935,7 @@
       <c r="N164" s="17" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="13" t="n">
+      <c r="A165" s="22" t="n">
         <v>45880</v>
       </c>
       <c r="B165" s="14" t="inlineStr">
@@ -7964,7 +7965,7 @@
       <c r="N165" s="17" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="13" t="n">
+      <c r="A166" s="22" t="n">
         <v>45881</v>
       </c>
       <c r="B166" s="14" t="inlineStr">
@@ -8014,7 +8015,7 @@
       <c r="N166" s="17" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="13" t="n">
+      <c r="A167" s="22" t="n">
         <v>45882</v>
       </c>
       <c r="B167" s="14" t="inlineStr">
@@ -8054,7 +8055,7 @@
       <c r="N167" s="17" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="13" t="n">
+      <c r="A168" s="22" t="n">
         <v>45883</v>
       </c>
       <c r="B168" s="14" t="inlineStr">
@@ -8104,7 +8105,7 @@
       <c r="N168" s="17" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="13" t="n">
+      <c r="A169" s="22" t="n">
         <v>45884</v>
       </c>
       <c r="B169" s="14" t="inlineStr">
@@ -8144,7 +8145,7 @@
       <c r="N169" s="17" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="13" t="n">
+      <c r="A170" s="22" t="n">
         <v>45887</v>
       </c>
       <c r="B170" s="14" t="inlineStr">
@@ -8194,7 +8195,7 @@
       <c r="N170" s="17" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="13" t="n">
+      <c r="A171" s="22" t="n">
         <v>45888</v>
       </c>
       <c r="B171" s="14" t="inlineStr">
@@ -8234,7 +8235,7 @@
       <c r="N171" s="17" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="13" t="n">
+      <c r="A172" s="22" t="n">
         <v>45889</v>
       </c>
       <c r="B172" s="14" t="inlineStr">
@@ -8274,7 +8275,7 @@
       <c r="N172" s="17" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="13" t="n">
+      <c r="A173" s="22" t="n">
         <v>45890</v>
       </c>
       <c r="B173" s="14" t="inlineStr">
@@ -8324,7 +8325,7 @@
       <c r="N173" s="17" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="13" t="n">
+      <c r="A174" s="22" t="n">
         <v>45891</v>
       </c>
       <c r="B174" s="14" t="inlineStr">
@@ -8374,7 +8375,7 @@
       <c r="N174" s="17" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="13" t="n">
+      <c r="A175" s="22" t="n">
         <v>45894</v>
       </c>
       <c r="B175" s="14" t="inlineStr">
@@ -8414,7 +8415,7 @@
       <c r="N175" s="17" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="13" t="n">
+      <c r="A176" s="22" t="n">
         <v>45895</v>
       </c>
       <c r="B176" s="14" t="inlineStr">
@@ -8454,7 +8455,7 @@
       <c r="N176" s="17" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="13" t="n">
+      <c r="A177" s="22" t="n">
         <v>45896</v>
       </c>
       <c r="B177" s="14" t="inlineStr">
@@ -8494,7 +8495,7 @@
       <c r="N177" s="17" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="13" t="n">
+      <c r="A178" s="22" t="n">
         <v>45897</v>
       </c>
       <c r="B178" s="14" t="inlineStr">
@@ -8544,7 +8545,7 @@
       <c r="N178" s="17" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="13" t="n">
+      <c r="A179" s="22" t="n">
         <v>45898</v>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -8594,7 +8595,7 @@
       <c r="N179" s="17" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="13" t="n">
+      <c r="A180" s="22" t="n">
         <v>45901</v>
       </c>
       <c r="B180" s="14" t="inlineStr">
@@ -8634,7 +8635,7 @@
       <c r="N180" s="17" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="13" t="n">
+      <c r="A181" s="22" t="n">
         <v>45902</v>
       </c>
       <c r="B181" s="14" t="inlineStr">
@@ -8684,7 +8685,7 @@
       <c r="N181" s="17" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="13" t="n">
+      <c r="A182" s="22" t="n">
         <v>45903</v>
       </c>
       <c r="B182" s="14" t="inlineStr">
@@ -8734,7 +8735,7 @@
       <c r="N182" s="17" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="13" t="n">
+      <c r="A183" s="22" t="n">
         <v>45904</v>
       </c>
       <c r="B183" s="14" t="inlineStr">
@@ -8784,7 +8785,7 @@
       <c r="N183" s="17" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="13" t="n">
+      <c r="A184" s="22" t="n">
         <v>45905</v>
       </c>
       <c r="B184" s="14" t="inlineStr">
@@ -8824,7 +8825,7 @@
       <c r="N184" s="17" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="13" t="n">
+      <c r="A185" s="22" t="n">
         <v>45908</v>
       </c>
       <c r="B185" s="14" t="inlineStr">
@@ -8874,7 +8875,7 @@
       <c r="N185" s="17" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="13" t="n">
+      <c r="A186" s="22" t="n">
         <v>45909</v>
       </c>
       <c r="B186" s="14" t="inlineStr">
@@ -8924,7 +8925,7 @@
       <c r="N186" s="17" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="13" t="n">
+      <c r="A187" s="22" t="n">
         <v>45910</v>
       </c>
       <c r="B187" s="14" t="inlineStr">
@@ -8974,7 +8975,7 @@
       <c r="N187" s="17" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="13" t="n">
+      <c r="A188" s="22" t="n">
         <v>45911</v>
       </c>
       <c r="B188" s="14" t="inlineStr">
@@ -9024,7 +9025,7 @@
       <c r="N188" s="17" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="13" t="n">
+      <c r="A189" s="22" t="n">
         <v>45912</v>
       </c>
       <c r="B189" s="14" t="inlineStr">
@@ -9074,7 +9075,7 @@
       <c r="N189" s="17" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="13" t="n">
+      <c r="A190" s="22" t="n">
         <v>45915</v>
       </c>
       <c r="B190" s="14" t="inlineStr">
@@ -9124,7 +9125,7 @@
       <c r="N190" s="17" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="13" t="n">
+      <c r="A191" s="22" t="n">
         <v>45916</v>
       </c>
       <c r="B191" s="14" t="inlineStr">
@@ -9164,7 +9165,7 @@
       <c r="N191" s="17" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="13" t="n">
+      <c r="A192" s="22" t="n">
         <v>45917</v>
       </c>
       <c r="B192" s="14" t="inlineStr">
@@ -9204,7 +9205,7 @@
       <c r="N192" s="17" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="13" t="n">
+      <c r="A193" s="22" t="n">
         <v>45918</v>
       </c>
       <c r="B193" s="14" t="inlineStr">
@@ -9254,7 +9255,7 @@
       <c r="N193" s="17" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="13" t="n">
+      <c r="A194" s="22" t="n">
         <v>45919</v>
       </c>
       <c r="B194" s="14" t="inlineStr">
@@ -9304,7 +9305,7 @@
       <c r="N194" s="17" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="13" t="n">
+      <c r="A195" s="22" t="n">
         <v>45922</v>
       </c>
       <c r="B195" s="14" t="inlineStr">
@@ -9354,7 +9355,7 @@
       <c r="N195" s="17" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="13" t="n">
+      <c r="A196" s="22" t="n">
         <v>45923</v>
       </c>
       <c r="B196" s="14" t="inlineStr">
@@ -9404,7 +9405,7 @@
       <c r="N196" s="17" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="13" t="n">
+      <c r="A197" s="22" t="n">
         <v>45924</v>
       </c>
       <c r="B197" s="14" t="inlineStr">
@@ -9444,7 +9445,7 @@
       <c r="N197" s="17" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="13" t="n">
+      <c r="A198" s="22" t="n">
         <v>45925</v>
       </c>
       <c r="B198" s="14" t="inlineStr">
@@ -9494,7 +9495,7 @@
       <c r="N198" s="17" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="13" t="n">
+      <c r="A199" s="22" t="n">
         <v>45926</v>
       </c>
       <c r="B199" s="14" t="inlineStr">
@@ -9544,7 +9545,7 @@
       <c r="N199" s="17" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="13" t="n">
+      <c r="A200" s="22" t="n">
         <v>45929</v>
       </c>
       <c r="B200" s="14" t="inlineStr">
@@ -9594,7 +9595,7 @@
       <c r="N200" s="17" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="13" t="n">
+      <c r="A201" s="22" t="n">
         <v>45930</v>
       </c>
       <c r="B201" s="14" t="inlineStr">
@@ -9634,7 +9635,7 @@
       <c r="N201" s="17" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="13" t="n">
+      <c r="A202" s="22" t="n">
         <v>45931</v>
       </c>
       <c r="B202" s="14" t="inlineStr">
@@ -9684,7 +9685,7 @@
       <c r="N202" s="17" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="13" t="n">
+      <c r="A203" s="22" t="n">
         <v>45932</v>
       </c>
       <c r="B203" s="14" t="inlineStr">
@@ -9734,7 +9735,7 @@
       <c r="N203" s="17" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="13" t="n">
+      <c r="A204" s="22" t="n">
         <v>45933</v>
       </c>
       <c r="B204" s="14" t="inlineStr">
@@ -9774,7 +9775,7 @@
       <c r="N204" s="17" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="13" t="n">
+      <c r="A205" s="22" t="n">
         <v>45936</v>
       </c>
       <c r="B205" s="14" t="inlineStr">
@@ -9824,7 +9825,7 @@
       <c r="N205" s="17" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="13" t="n">
+      <c r="A206" s="22" t="n">
         <v>45937</v>
       </c>
       <c r="B206" s="14" t="inlineStr">
@@ -9864,7 +9865,7 @@
       <c r="N206" s="17" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="13" t="n">
+      <c r="A207" s="22" t="n">
         <v>45938</v>
       </c>
       <c r="B207" s="14" t="inlineStr">
@@ -9914,7 +9915,7 @@
       <c r="N207" s="17" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="13" t="n">
+      <c r="A208" s="22" t="n">
         <v>45939</v>
       </c>
       <c r="B208" s="14" t="inlineStr">
@@ -9964,7 +9965,7 @@
       <c r="N208" s="17" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="13" t="n">
+      <c r="A209" s="22" t="n">
         <v>45940</v>
       </c>
       <c r="B209" s="14" t="inlineStr">
@@ -10014,7 +10015,7 @@
       <c r="N209" s="17" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="13" t="n">
+      <c r="A210" s="22" t="n">
         <v>45943</v>
       </c>
       <c r="B210" s="14" t="inlineStr">
@@ -10064,7 +10065,7 @@
       <c r="N210" s="17" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="13" t="n">
+      <c r="A211" s="22" t="n">
         <v>45944</v>
       </c>
       <c r="B211" s="14" t="inlineStr">
@@ -10104,7 +10105,7 @@
       <c r="N211" s="17" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="13" t="n">
+      <c r="A212" s="22" t="n">
         <v>45945</v>
       </c>
       <c r="B212" s="14" t="inlineStr">
@@ -10154,7 +10155,7 @@
       <c r="N212" s="17" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="13" t="n">
+      <c r="A213" s="22" t="n">
         <v>45946</v>
       </c>
       <c r="B213" s="14" t="inlineStr">
@@ -10184,7 +10185,7 @@
       <c r="N213" s="17" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="13" t="n">
+      <c r="A214" s="22" t="n">
         <v>45947</v>
       </c>
       <c r="B214" s="14" t="inlineStr">
@@ -10234,7 +10235,7 @@
       <c r="N214" s="17" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="13" t="n">
+      <c r="A215" s="22" t="n">
         <v>45950</v>
       </c>
       <c r="B215" s="14" t="inlineStr">
@@ -10284,7 +10285,7 @@
       <c r="N215" s="17" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="13" t="n">
+      <c r="A216" s="22" t="n">
         <v>45951</v>
       </c>
       <c r="B216" s="14" t="inlineStr">
@@ -10334,7 +10335,7 @@
       <c r="N216" s="17" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="13" t="n">
+      <c r="A217" s="22" t="n">
         <v>45952</v>
       </c>
       <c r="B217" s="14" t="inlineStr">
@@ -10384,7 +10385,7 @@
       <c r="N217" s="17" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="13" t="n">
+      <c r="A218" s="22" t="n">
         <v>45953</v>
       </c>
       <c r="B218" s="14" t="inlineStr">
@@ -10424,7 +10425,7 @@
       <c r="N218" s="17" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="13" t="n">
+      <c r="A219" s="22" t="n">
         <v>45954</v>
       </c>
       <c r="B219" s="14" t="inlineStr">
@@ -10474,7 +10475,7 @@
       <c r="N219" s="17" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="13" t="n">
+      <c r="A220" s="22" t="n">
         <v>45957</v>
       </c>
       <c r="B220" s="14" t="inlineStr">
@@ -10524,7 +10525,7 @@
       <c r="N220" s="17" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="13" t="n">
+      <c r="A221" s="22" t="n">
         <v>45958</v>
       </c>
       <c r="B221" s="14" t="inlineStr">
@@ -10574,7 +10575,7 @@
       <c r="N221" s="17" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="13" t="n">
+      <c r="A222" s="22" t="n">
         <v>45959</v>
       </c>
       <c r="B222" s="14" t="inlineStr">
@@ -10624,7 +10625,7 @@
       <c r="N222" s="17" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="13" t="n">
+      <c r="A223" s="22" t="n">
         <v>45960</v>
       </c>
       <c r="B223" s="14" t="inlineStr">
@@ -10664,7 +10665,7 @@
       <c r="N223" s="17" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="13" t="n">
+      <c r="A224" s="22" t="n">
         <v>45961</v>
       </c>
       <c r="B224" s="14" t="inlineStr">
@@ -10704,7 +10705,7 @@
       <c r="N224" s="17" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="13" t="n">
+      <c r="A225" s="22" t="n">
         <v>45964</v>
       </c>
       <c r="B225" s="14" t="inlineStr">
@@ -10754,7 +10755,7 @@
       <c r="N225" s="17" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="13" t="n">
+      <c r="A226" s="22" t="n">
         <v>45965</v>
       </c>
       <c r="B226" s="14" t="inlineStr">
@@ -10804,7 +10805,7 @@
       <c r="N226" s="17" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="13" t="n">
+      <c r="A227" s="22" t="n">
         <v>45966</v>
       </c>
       <c r="B227" s="14" t="inlineStr">
@@ -10844,7 +10845,7 @@
       <c r="N227" s="17" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="13" t="n">
+      <c r="A228" s="22" t="n">
         <v>45967</v>
       </c>
       <c r="B228" s="14" t="inlineStr">
@@ -10894,7 +10895,7 @@
       <c r="N228" s="17" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="13" t="n">
+      <c r="A229" s="22" t="n">
         <v>45968</v>
       </c>
       <c r="B229" s="14" t="inlineStr">
@@ -10944,7 +10945,7 @@
       <c r="N229" s="17" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="13" t="n">
+      <c r="A230" s="22" t="n">
         <v>45971</v>
       </c>
       <c r="B230" s="14" t="inlineStr">
@@ -10994,7 +10995,7 @@
       <c r="N230" s="17" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="13" t="n">
+      <c r="A231" s="22" t="n">
         <v>45972</v>
       </c>
       <c r="B231" s="14" t="inlineStr">
@@ -11034,7 +11035,7 @@
       <c r="N231" s="17" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="13" t="n">
+      <c r="A232" s="22" t="n">
         <v>45973</v>
       </c>
       <c r="B232" s="14" t="inlineStr">
@@ -11084,7 +11085,7 @@
       <c r="N232" s="17" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="13" t="n">
+      <c r="A233" s="22" t="n">
         <v>45974</v>
       </c>
       <c r="B233" s="14" t="inlineStr">
@@ -11134,7 +11135,7 @@
       <c r="N233" s="17" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="13" t="n">
+      <c r="A234" s="22" t="n">
         <v>45975</v>
       </c>
       <c r="B234" s="14" t="inlineStr">
@@ -11184,7 +11185,7 @@
       <c r="N234" s="17" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="13" t="n">
+      <c r="A235" s="22" t="n">
         <v>45978</v>
       </c>
       <c r="B235" s="14" t="inlineStr">
@@ -11224,7 +11225,7 @@
       <c r="N235" s="17" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="13" t="n">
+      <c r="A236" s="22" t="n">
         <v>45979</v>
       </c>
       <c r="B236" s="14" t="inlineStr">
@@ -11274,7 +11275,7 @@
       <c r="N236" s="17" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="13" t="n">
+      <c r="A237" s="22" t="n">
         <v>45980</v>
       </c>
       <c r="B237" s="14" t="inlineStr">
@@ -11324,7 +11325,7 @@
       <c r="N237" s="17" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="13" t="n">
+      <c r="A238" s="22" t="n">
         <v>45981</v>
       </c>
       <c r="B238" s="14" t="inlineStr">
@@ -11364,7 +11365,7 @@
       <c r="N238" s="17" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="13" t="n">
+      <c r="A239" s="22" t="n">
         <v>45982</v>
       </c>
       <c r="B239" s="14" t="inlineStr">
@@ -11414,7 +11415,7 @@
       <c r="N239" s="17" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="13" t="n">
+      <c r="A240" s="22" t="n">
         <v>45985</v>
       </c>
       <c r="B240" s="14" t="inlineStr">
@@ -11454,7 +11455,7 @@
       <c r="N240" s="17" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="13" t="n">
+      <c r="A241" s="22" t="n">
         <v>45986</v>
       </c>
       <c r="B241" s="14" t="inlineStr">
@@ -11494,7 +11495,7 @@
       <c r="N241" s="17" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="13" t="n">
+      <c r="A242" s="22" t="n">
         <v>45987</v>
       </c>
       <c r="B242" s="14" t="inlineStr">
@@ -11544,7 +11545,7 @@
       <c r="N242" s="17" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="13" t="n">
+      <c r="A243" s="22" t="n">
         <v>45988</v>
       </c>
       <c r="B243" s="14" t="inlineStr">
@@ -11594,7 +11595,7 @@
       <c r="N243" s="17" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="13" t="n">
+      <c r="A244" s="22" t="n">
         <v>45989</v>
       </c>
       <c r="B244" s="14" t="inlineStr">
@@ -11634,7 +11635,7 @@
       <c r="N244" s="17" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="13" t="n">
+      <c r="A245" s="22" t="n">
         <v>45992</v>
       </c>
       <c r="B245" s="14" t="inlineStr">
@@ -11684,7 +11685,7 @@
       <c r="N245" s="17" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="13" t="n">
+      <c r="A246" s="22" t="n">
         <v>45993</v>
       </c>
       <c r="B246" s="14" t="inlineStr">
@@ -11734,7 +11735,7 @@
       <c r="N246" s="17" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="13" t="n">
+      <c r="A247" s="22" t="n">
         <v>45994</v>
       </c>
       <c r="B247" s="14" t="inlineStr">
@@ -11784,7 +11785,7 @@
       <c r="N247" s="17" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="13" t="n">
+      <c r="A248" s="22" t="n">
         <v>45995</v>
       </c>
       <c r="B248" s="14" t="inlineStr">
@@ -11834,7 +11835,7 @@
       <c r="N248" s="17" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="13" t="n">
+      <c r="A249" s="22" t="n">
         <v>45996</v>
       </c>
       <c r="B249" s="14" t="inlineStr">
@@ -11884,7 +11885,7 @@
       <c r="N249" s="17" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="13" t="n">
+      <c r="A250" s="22" t="n">
         <v>45999</v>
       </c>
       <c r="B250" s="14" t="inlineStr">
@@ -11934,7 +11935,7 @@
       <c r="N250" s="17" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="13" t="n">
+      <c r="A251" s="22" t="n">
         <v>46000</v>
       </c>
       <c r="B251" s="14" t="inlineStr">
@@ -11984,7 +11985,7 @@
       <c r="N251" s="17" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="13" t="n">
+      <c r="A252" s="22" t="n">
         <v>46001</v>
       </c>
       <c r="B252" s="14" t="inlineStr">
@@ -12034,7 +12035,7 @@
       <c r="N252" s="17" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="13" t="n">
+      <c r="A253" s="22" t="n">
         <v>46002</v>
       </c>
       <c r="B253" s="14" t="inlineStr">
@@ -12074,7 +12075,7 @@
       <c r="N253" s="17" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="13" t="n">
+      <c r="A254" s="22" t="n">
         <v>46003</v>
       </c>
       <c r="B254" s="14" t="inlineStr">
@@ -12124,7 +12125,7 @@
       <c r="N254" s="17" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="13" t="n">
+      <c r="A255" s="22" t="n">
         <v>46006</v>
       </c>
       <c r="B255" s="14" t="inlineStr">
@@ -12174,7 +12175,7 @@
       <c r="N255" s="17" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="13" t="n">
+      <c r="A256" s="22" t="n">
         <v>46007</v>
       </c>
       <c r="B256" s="14" t="inlineStr">
@@ -12224,7 +12225,7 @@
       <c r="N256" s="17" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="13" t="n">
+      <c r="A257" s="22" t="n">
         <v>46008</v>
       </c>
       <c r="B257" s="14" t="inlineStr">
@@ -12274,7 +12275,7 @@
       <c r="N257" s="17" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="13" t="n">
+      <c r="A258" s="22" t="n">
         <v>46009</v>
       </c>
       <c r="B258" s="14" t="inlineStr">
@@ -12324,7 +12325,7 @@
       <c r="N258" s="17" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="13" t="n">
+      <c r="A259" s="22" t="n">
         <v>46010</v>
       </c>
       <c r="B259" s="14" t="inlineStr">
@@ -12374,7 +12375,7 @@
       <c r="N259" s="17" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="13" t="n">
+      <c r="A260" s="22" t="n">
         <v>46013</v>
       </c>
       <c r="B260" s="14" t="inlineStr">
@@ -12414,7 +12415,7 @@
       <c r="N260" s="17" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="13" t="n">
+      <c r="A261" s="22" t="n">
         <v>46014</v>
       </c>
       <c r="B261" s="14" t="inlineStr">
@@ -12464,7 +12465,7 @@
       <c r="N261" s="17" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="13" t="n">
+      <c r="A262" s="22" t="n">
         <v>46015</v>
       </c>
       <c r="B262" s="14" t="inlineStr">
@@ -12514,7 +12515,7 @@
       <c r="N262" s="17" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="11" t="n">
+      <c r="A263" s="21" t="n">
         <v>46016</v>
       </c>
       <c r="B263" s="12" t="inlineStr">
@@ -12544,7 +12545,7 @@
       <c r="N263" s="12" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="13" t="n">
+      <c r="A264" s="22" t="n">
         <v>46017</v>
       </c>
       <c r="B264" s="14" t="inlineStr">
@@ -12584,7 +12585,7 @@
       <c r="N264" s="17" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="13" t="n">
+      <c r="A265" s="22" t="n">
         <v>46020</v>
       </c>
       <c r="B265" s="14" t="inlineStr">
@@ -12624,7 +12625,7 @@
       <c r="N265" s="17" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="13" t="n">
+      <c r="A266" s="22" t="n">
         <v>46021</v>
       </c>
       <c r="B266" s="14" t="inlineStr">
@@ -12674,7 +12675,7 @@
       <c r="N266" s="17" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="13" t="n">
+      <c r="A267" s="22" t="n">
         <v>46022</v>
       </c>
       <c r="B267" s="14" t="inlineStr">
@@ -12713,10 +12714,16 @@
       <c r="M267" s="16" t="n"/>
       <c r="N267" s="17" t="n"/>
     </row>
+    <row r="268"/>
     <row r="269">
       <c r="A269" s="19" t="inlineStr">
         <is>
           <t>RESUMEN (automático)</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>(las cifras aparecen al abrir el fichero en Excel o Google Sheets)</t>
         </is>
       </c>
     </row>

--- a/josh_auditoria_manual_2025.xlsx
+++ b/josh_auditoria_manual_2025.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -139,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,9 +158,9 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -171,8 +172,6 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +581,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Modelos generados con la lógica del indicador JoshModels_H1: un modelo máximo por sesión (Londres: LR2.1 &gt; LR1 &gt; A1 &gt; LR2.2 · NY: NYR2 &gt; NYC1 &gt; NYR1), rango de Asia 17:00–00:00 NY, sin OSOK, sin NYC2, sin News Protocol. Horas en NY.</t>
+          <t>Modelos generados con la lógica del indicador JoshModels_H1: un modelo máximo por sesión (Londres: LR2.1 &gt; LR1 &gt; A1 &gt; LR2.2 · NY: NYR2 &gt; NYC1 &gt; NYR1), rango de Asia 17:00–00:00 NY, todas las señales exigen confirmación (cierre de vuelta dentro), riesgo mínimo 5 pips, sin OSOK, sin NYC2, sin News Protocol. Horas en NY.</t>
         </is>
       </c>
     </row>
@@ -725,7 +724,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="11" t="n">
         <v>45658</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -755,7 +754,7 @@
       <c r="N7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="13" t="n">
         <v>45659</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -785,7 +784,7 @@
       <c r="N8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="13" t="n">
         <v>45660</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -795,22 +794,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>1.02745</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="14" t="n"/>
       <c r="G9" s="16" t="n"/>
       <c r="H9" s="17" t="n"/>
       <c r="I9" s="14" t="inlineStr">
@@ -825,7 +814,7 @@
       <c r="N9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="13" t="n">
         <v>45663</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -835,22 +824,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>1.03182</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="14" t="n"/>
       <c r="G10" s="16" t="n"/>
       <c r="H10" s="17" t="n"/>
       <c r="I10" s="14" t="inlineStr">
@@ -875,7 +854,7 @@
       <c r="N10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="13" t="n">
         <v>45664</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -885,22 +864,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>1.03943</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="14" t="n"/>
       <c r="G11" s="16" t="n"/>
       <c r="H11" s="17" t="n"/>
       <c r="I11" s="14" t="inlineStr">
@@ -925,7 +894,7 @@
       <c r="N11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="13" t="n">
         <v>45665</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -965,7 +934,7 @@
       <c r="N12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="13" t="n">
         <v>45666</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -975,47 +944,37 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1.03049</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="14" t="n"/>
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="17" t="n"/>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>largo</t>
+          <t>corto</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L13" s="18" t="n">
-        <v>1.02836</v>
+        <v>1.0319</v>
       </c>
       <c r="M13" s="16" t="n"/>
       <c r="N13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="13" t="n">
         <v>45667</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -1065,7 +1024,7 @@
       <c r="N14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="13" t="n">
         <v>45670</v>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -1075,22 +1034,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1.02076</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="14" t="n"/>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="17" t="n"/>
       <c r="I15" s="14" t="inlineStr">
@@ -1105,7 +1054,7 @@
       <c r="N15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="13" t="n">
         <v>45671</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -1135,7 +1084,7 @@
       <c r="N16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="13" t="n">
         <v>45672</v>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -1185,7 +1134,7 @@
       <c r="N17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="13" t="n">
         <v>45673</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -1235,7 +1184,7 @@
       <c r="N18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="13" t="n">
         <v>45674</v>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1285,7 +1234,7 @@
       <c r="N19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n">
+      <c r="A20" s="13" t="n">
         <v>45677</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -1295,22 +1244,12 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1.03071</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="14" t="n"/>
       <c r="G20" s="16" t="n"/>
       <c r="H20" s="17" t="n"/>
       <c r="I20" s="14" t="inlineStr">
@@ -1325,7 +1264,7 @@
       <c r="N20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n">
+      <c r="A21" s="13" t="n">
         <v>45678</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -1335,47 +1274,27 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1.03528</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="14" t="n"/>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="17" t="n"/>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K21" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>1.0342</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="14" t="n"/>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n">
+      <c r="A22" s="13" t="n">
         <v>45679</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -1385,22 +1304,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>1.04334</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="14" t="n"/>
       <c r="G22" s="16" t="n"/>
       <c r="H22" s="17" t="n"/>
       <c r="I22" s="14" t="inlineStr">
@@ -1415,7 +1324,7 @@
       <c r="N22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n">
+      <c r="A23" s="13" t="n">
         <v>45680</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1425,7 +1334,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -1435,7 +1344,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F23" s="18" t="n">
@@ -1445,27 +1354,17 @@
       <c r="H23" s="17" t="n"/>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K23" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>1.0406</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="14" t="n"/>
       <c r="M23" s="16" t="n"/>
       <c r="N23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n">
+      <c r="A24" s="13" t="n">
         <v>45681</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -1475,22 +1374,12 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1.04537</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="14" t="n"/>
       <c r="G24" s="16" t="n"/>
       <c r="H24" s="17" t="n"/>
       <c r="I24" s="14" t="inlineStr">
@@ -1505,7 +1394,7 @@
       <c r="N24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n">
+      <c r="A25" s="13" t="n">
         <v>45684</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -1515,21 +1404,21 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR1</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F25" s="18" t="n">
-        <v>1.04851</v>
+        <v>1.04588</v>
       </c>
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="17" t="n"/>
@@ -1555,7 +1444,7 @@
       <c r="N25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n">
+      <c r="A26" s="13" t="n">
         <v>45685</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -1565,7 +1454,7 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -1575,7 +1464,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F26" s="18" t="n">
@@ -1595,7 +1484,7 @@
       <c r="N26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n">
+      <c r="A27" s="13" t="n">
         <v>45686</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -1645,7 +1534,7 @@
       <c r="N27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n">
+      <c r="A28" s="13" t="n">
         <v>45687</v>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -1695,7 +1584,7 @@
       <c r="N28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n">
+      <c r="A29" s="13" t="n">
         <v>45688</v>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1745,7 +1634,7 @@
       <c r="N29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n">
+      <c r="A30" s="13" t="n">
         <v>45691</v>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -1785,7 +1674,7 @@
       <c r="N30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n">
+      <c r="A31" s="13" t="n">
         <v>45692</v>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -1835,7 +1724,7 @@
       <c r="N31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n">
+      <c r="A32" s="13" t="n">
         <v>45693</v>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -1845,22 +1734,12 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>1.03864</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="14" t="n"/>
       <c r="G32" s="16" t="n"/>
       <c r="H32" s="17" t="n"/>
       <c r="I32" s="14" t="inlineStr">
@@ -1875,7 +1754,7 @@
       <c r="N32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n">
+      <c r="A33" s="13" t="n">
         <v>45694</v>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1885,22 +1764,12 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>1.03852</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="14" t="n"/>
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="17" t="n"/>
       <c r="I33" s="14" t="inlineStr">
@@ -1915,7 +1784,7 @@
       <c r="N33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n">
+      <c r="A34" s="13" t="n">
         <v>45695</v>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -1965,7 +1834,7 @@
       <c r="N34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="13" t="n">
         <v>45698</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -2015,7 +1884,7 @@
       <c r="N35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n">
+      <c r="A36" s="13" t="n">
         <v>45699</v>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -2055,7 +1924,7 @@
       <c r="N36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n">
+      <c r="A37" s="13" t="n">
         <v>45700</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -2065,22 +1934,12 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>1.03677</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="14" t="n"/>
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="17" t="n"/>
       <c r="I37" s="14" t="inlineStr">
@@ -2095,7 +1954,7 @@
       <c r="N37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n">
+      <c r="A38" s="13" t="n">
         <v>45701</v>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -2145,7 +2004,7 @@
       <c r="N38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n">
+      <c r="A39" s="13" t="n">
         <v>45702</v>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -2185,7 +2044,7 @@
       <c r="N39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n">
+      <c r="A40" s="13" t="n">
         <v>45705</v>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -2195,22 +2054,12 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>1.04847</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="14" t="n"/>
       <c r="G40" s="16" t="n"/>
       <c r="H40" s="17" t="n"/>
       <c r="I40" s="14" t="inlineStr">
@@ -2235,7 +2084,7 @@
       <c r="N40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n">
+      <c r="A41" s="13" t="n">
         <v>45706</v>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -2275,7 +2124,7 @@
       <c r="N41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n">
+      <c r="A42" s="13" t="n">
         <v>45707</v>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -2325,7 +2174,7 @@
       <c r="N42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n">
+      <c r="A43" s="13" t="n">
         <v>45708</v>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -2335,22 +2184,12 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>1.04375</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="14" t="n"/>
       <c r="G43" s="16" t="n"/>
       <c r="H43" s="17" t="n"/>
       <c r="I43" s="14" t="inlineStr">
@@ -2365,7 +2204,7 @@
       <c r="N43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n">
+      <c r="A44" s="13" t="n">
         <v>45709</v>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -2375,22 +2214,12 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>1.04843</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="14" t="n"/>
       <c r="G44" s="16" t="n"/>
       <c r="H44" s="17" t="n"/>
       <c r="I44" s="14" t="inlineStr">
@@ -2405,7 +2234,7 @@
       <c r="N44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n">
+      <c r="A45" s="13" t="n">
         <v>45712</v>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -2445,7 +2274,7 @@
       <c r="N45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n">
+      <c r="A46" s="13" t="n">
         <v>45713</v>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -2485,7 +2314,7 @@
       <c r="N46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n">
+      <c r="A47" s="13" t="n">
         <v>45714</v>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -2525,7 +2354,7 @@
       <c r="N47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n">
+      <c r="A48" s="13" t="n">
         <v>45715</v>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -2565,7 +2394,7 @@
       <c r="N48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n">
+      <c r="A49" s="13" t="n">
         <v>45716</v>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -2585,7 +2414,7 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F49" s="18" t="n">
@@ -2615,7 +2444,7 @@
       <c r="N49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n">
+      <c r="A50" s="13" t="n">
         <v>45719</v>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -2625,47 +2454,27 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>1.03992</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="14" t="n"/>
       <c r="G50" s="16" t="n"/>
       <c r="H50" s="17" t="n"/>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>NYR1</t>
-        </is>
-      </c>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K50" s="15" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="L50" s="18" t="n">
-        <v>1.04762</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="15" t="n"/>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="14" t="n"/>
       <c r="M50" s="16" t="n"/>
       <c r="N50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n">
+      <c r="A51" s="13" t="n">
         <v>45720</v>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -2715,7 +2524,7 @@
       <c r="N51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n">
+      <c r="A52" s="13" t="n">
         <v>45721</v>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -2725,27 +2534,17 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>1.06369</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="14" t="n"/>
       <c r="G52" s="16" t="n"/>
       <c r="H52" s="17" t="n"/>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J52" s="15" t="inlineStr">
@@ -2755,17 +2554,17 @@
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L52" s="18" t="n">
-        <v>1.0722</v>
+        <v>1.07225</v>
       </c>
       <c r="M52" s="16" t="n"/>
       <c r="N52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n">
+      <c r="A53" s="13" t="n">
         <v>45722</v>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -2815,7 +2614,7 @@
       <c r="N53" s="17" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n">
+      <c r="A54" s="13" t="n">
         <v>45723</v>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -2825,27 +2624,17 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>1.08146</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="14" t="n"/>
       <c r="G54" s="16" t="n"/>
       <c r="H54" s="17" t="n"/>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J54" s="15" t="inlineStr">
@@ -2855,17 +2644,17 @@
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L54" s="18" t="n">
-        <v>1.08714</v>
+        <v>1.08884</v>
       </c>
       <c r="M54" s="16" t="n"/>
       <c r="N54" s="17" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n">
+      <c r="A55" s="13" t="n">
         <v>45726</v>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -2875,7 +2664,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
@@ -2885,7 +2674,7 @@
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F55" s="18" t="n">
@@ -2895,27 +2684,17 @@
       <c r="H55" s="17" t="n"/>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J55" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K55" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L55" s="18" t="n">
-        <v>1.08051</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="15" t="n"/>
+      <c r="L55" s="14" t="n"/>
       <c r="M55" s="16" t="n"/>
       <c r="N55" s="17" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n">
+      <c r="A56" s="13" t="n">
         <v>45727</v>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -2925,27 +2704,17 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>1.08615</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="14" t="n"/>
       <c r="G56" s="16" t="n"/>
       <c r="H56" s="17" t="n"/>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J56" s="15" t="inlineStr">
@@ -2955,17 +2724,17 @@
       </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1.09207</v>
+        <v>1.09306</v>
       </c>
       <c r="M56" s="16" t="n"/>
       <c r="N56" s="17" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n">
+      <c r="A57" s="13" t="n">
         <v>45728</v>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -3015,7 +2784,7 @@
       <c r="N57" s="17" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n">
+      <c r="A58" s="13" t="n">
         <v>45729</v>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -3025,22 +2794,12 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>1.08816</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="n"/>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="14" t="n"/>
       <c r="G58" s="16" t="n"/>
       <c r="H58" s="17" t="n"/>
       <c r="I58" s="14" t="inlineStr">
@@ -3065,7 +2824,7 @@
       <c r="N58" s="17" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n">
+      <c r="A59" s="13" t="n">
         <v>45730</v>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -3075,7 +2834,7 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
@@ -3089,33 +2848,23 @@
         </is>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1.08341</v>
+        <v>1.08304</v>
       </c>
       <c r="G59" s="16" t="n"/>
       <c r="H59" s="17" t="n"/>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J59" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K59" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L59" s="18" t="n">
-        <v>1.08304</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="15" t="n"/>
+      <c r="K59" s="15" t="n"/>
+      <c r="L59" s="14" t="n"/>
       <c r="M59" s="16" t="n"/>
       <c r="N59" s="17" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n">
+      <c r="A60" s="13" t="n">
         <v>45733</v>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -3165,7 +2914,7 @@
       <c r="N60" s="17" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n">
+      <c r="A61" s="13" t="n">
         <v>45734</v>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -3205,7 +2954,7 @@
       <c r="N61" s="17" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n">
+      <c r="A62" s="13" t="n">
         <v>45735</v>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -3215,47 +2964,27 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>1.09279</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="14" t="n"/>
       <c r="G62" s="16" t="n"/>
       <c r="H62" s="17" t="n"/>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J62" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K62" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L62" s="18" t="n">
-        <v>1.08731</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="15" t="n"/>
+      <c r="K62" s="15" t="n"/>
+      <c r="L62" s="14" t="n"/>
       <c r="M62" s="16" t="n"/>
       <c r="N62" s="17" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n">
+      <c r="A63" s="13" t="n">
         <v>45736</v>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -3265,22 +2994,12 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>1.09003</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="14" t="n"/>
       <c r="G63" s="16" t="n"/>
       <c r="H63" s="17" t="n"/>
       <c r="I63" s="14" t="inlineStr">
@@ -3295,7 +3014,7 @@
       <c r="N63" s="17" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="n">
+      <c r="A64" s="13" t="n">
         <v>45737</v>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -3345,7 +3064,7 @@
       <c r="N64" s="17" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="n">
+      <c r="A65" s="13" t="n">
         <v>45740</v>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -3395,7 +3114,7 @@
       <c r="N65" s="17" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="n">
+      <c r="A66" s="13" t="n">
         <v>45741</v>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -3405,7 +3124,7 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
@@ -3415,7 +3134,7 @@
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F66" s="18" t="n">
@@ -3425,27 +3144,17 @@
       <c r="H66" s="17" t="n"/>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J66" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K66" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L66" s="18" t="n">
-        <v>1.07767</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="15" t="n"/>
+      <c r="K66" s="15" t="n"/>
+      <c r="L66" s="14" t="n"/>
       <c r="M66" s="16" t="n"/>
       <c r="N66" s="17" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="n">
+      <c r="A67" s="13" t="n">
         <v>45742</v>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -3455,47 +3164,37 @@
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F67" s="18" t="n">
-        <v>1.0797</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="n"/>
+      <c r="E67" s="15" t="n"/>
+      <c r="F67" s="14" t="n"/>
       <c r="G67" s="16" t="n"/>
       <c r="H67" s="17" t="n"/>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L67" s="18" t="n">
-        <v>1.08025</v>
+        <v>1.07729</v>
       </c>
       <c r="M67" s="16" t="n"/>
       <c r="N67" s="17" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n">
+      <c r="A68" s="13" t="n">
         <v>45743</v>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -3525,7 +3224,7 @@
       <c r="N68" s="17" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="n">
+      <c r="A69" s="13" t="n">
         <v>45744</v>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -3535,7 +3234,7 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>LR2.1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
@@ -3549,7 +3248,7 @@
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>1.07824</v>
+        <v>1.07815</v>
       </c>
       <c r="G69" s="16" t="n"/>
       <c r="H69" s="17" t="n"/>
@@ -3575,7 +3274,7 @@
       <c r="N69" s="17" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="n">
+      <c r="A70" s="13" t="n">
         <v>45747</v>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -3625,7 +3324,7 @@
       <c r="N70" s="17" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="n">
+      <c r="A71" s="13" t="n">
         <v>45748</v>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -3635,22 +3334,12 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>1.08129</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="n"/>
+      <c r="E71" s="15" t="n"/>
+      <c r="F71" s="14" t="n"/>
       <c r="G71" s="16" t="n"/>
       <c r="H71" s="17" t="n"/>
       <c r="I71" s="14" t="inlineStr">
@@ -3665,7 +3354,7 @@
       <c r="N71" s="17" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="n">
+      <c r="A72" s="13" t="n">
         <v>45749</v>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -3675,47 +3364,27 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>1.0785</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n"/>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="14" t="n"/>
       <c r="G72" s="16" t="n"/>
       <c r="H72" s="17" t="n"/>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
-        </is>
-      </c>
-      <c r="J72" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K72" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L72" s="18" t="n">
-        <v>1.08061</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="n"/>
+      <c r="K72" s="15" t="n"/>
+      <c r="L72" s="14" t="n"/>
       <c r="M72" s="16" t="n"/>
       <c r="N72" s="17" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="n">
+      <c r="A73" s="13" t="n">
         <v>45750</v>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -3725,22 +3394,12 @@
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>1.09244</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="14" t="n"/>
       <c r="G73" s="16" t="n"/>
       <c r="H73" s="17" t="n"/>
       <c r="I73" s="14" t="inlineStr">
@@ -3755,7 +3414,7 @@
       <c r="N73" s="17" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="n">
+      <c r="A74" s="13" t="n">
         <v>45751</v>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -3805,7 +3464,7 @@
       <c r="N74" s="17" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="n">
+      <c r="A75" s="13" t="n">
         <v>45754</v>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -3815,7 +3474,7 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
@@ -3825,7 +3484,7 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
@@ -3835,27 +3494,17 @@
       <c r="H75" s="17" t="n"/>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J75" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K75" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L75" s="18" t="n">
-        <v>1.10498</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="15" t="n"/>
+      <c r="K75" s="15" t="n"/>
+      <c r="L75" s="14" t="n"/>
       <c r="M75" s="16" t="n"/>
       <c r="N75" s="17" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="n">
+      <c r="A76" s="13" t="n">
         <v>45755</v>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -3905,7 +3554,7 @@
       <c r="N76" s="17" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="n">
+      <c r="A77" s="13" t="n">
         <v>45756</v>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -3955,7 +3604,7 @@
       <c r="N77" s="17" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="n">
+      <c r="A78" s="13" t="n">
         <v>45757</v>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -3995,7 +3644,7 @@
       <c r="N78" s="17" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="n">
+      <c r="A79" s="13" t="n">
         <v>45758</v>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -4005,22 +3654,12 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>1.13852</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="n"/>
+      <c r="E79" s="15" t="n"/>
+      <c r="F79" s="14" t="n"/>
       <c r="G79" s="16" t="n"/>
       <c r="H79" s="17" t="n"/>
       <c r="I79" s="14" t="inlineStr">
@@ -4035,7 +3674,7 @@
       <c r="N79" s="17" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="n">
+      <c r="A80" s="13" t="n">
         <v>45761</v>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -4085,7 +3724,7 @@
       <c r="N80" s="17" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="n">
+      <c r="A81" s="13" t="n">
         <v>45762</v>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -4135,7 +3774,7 @@
       <c r="N81" s="17" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="n">
+      <c r="A82" s="13" t="n">
         <v>45763</v>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -4145,47 +3784,27 @@
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F82" s="18" t="n">
-        <v>1.13433</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="n"/>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="14" t="n"/>
       <c r="G82" s="16" t="n"/>
       <c r="H82" s="17" t="n"/>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J82" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K82" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>1.1392</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="n"/>
+      <c r="K82" s="15" t="n"/>
+      <c r="L82" s="14" t="n"/>
       <c r="M82" s="16" t="n"/>
       <c r="N82" s="17" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="n">
+      <c r="A83" s="13" t="n">
         <v>45764</v>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -4235,7 +3854,7 @@
       <c r="N83" s="17" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="n">
+      <c r="A84" s="13" t="n">
         <v>45765</v>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -4285,7 +3904,7 @@
       <c r="N84" s="17" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="n">
+      <c r="A85" s="13" t="n">
         <v>45768</v>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -4315,27 +3934,27 @@
       <c r="H85" s="17" t="n"/>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J85" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1.15474</v>
+        <v>1.15012</v>
       </c>
       <c r="M85" s="16" t="n"/>
       <c r="N85" s="17" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="n">
+      <c r="A86" s="13" t="n">
         <v>45769</v>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -4375,7 +3994,7 @@
       <c r="N86" s="17" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="n">
+      <c r="A87" s="13" t="n">
         <v>45770</v>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -4415,7 +4034,7 @@
       <c r="N87" s="17" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="n">
+      <c r="A88" s="13" t="n">
         <v>45771</v>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -4425,22 +4044,12 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F88" s="18" t="n">
-        <v>1.13574</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="14" t="n"/>
       <c r="G88" s="16" t="n"/>
       <c r="H88" s="17" t="n"/>
       <c r="I88" s="14" t="inlineStr">
@@ -4455,7 +4064,7 @@
       <c r="N88" s="17" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="n">
+      <c r="A89" s="13" t="n">
         <v>45772</v>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -4505,7 +4114,7 @@
       <c r="N89" s="17" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="n">
+      <c r="A90" s="13" t="n">
         <v>45775</v>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -4555,7 +4164,7 @@
       <c r="N90" s="17" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="n">
+      <c r="A91" s="13" t="n">
         <v>45776</v>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -4595,17 +4204,17 @@
       </c>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L91" s="18" t="n">
-        <v>1.14144</v>
+        <v>1.14169</v>
       </c>
       <c r="M91" s="16" t="n"/>
       <c r="N91" s="17" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="n">
+      <c r="A92" s="13" t="n">
         <v>45777</v>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -4635,7 +4244,7 @@
       <c r="N92" s="17" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="n">
+      <c r="A93" s="13" t="n">
         <v>45778</v>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -4685,7 +4294,7 @@
       <c r="N93" s="17" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="n">
+      <c r="A94" s="13" t="n">
         <v>45779</v>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -4695,22 +4304,12 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F94" s="18" t="n">
-        <v>1.13153</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="n"/>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="14" t="n"/>
       <c r="G94" s="16" t="n"/>
       <c r="H94" s="17" t="n"/>
       <c r="I94" s="14" t="inlineStr">
@@ -4735,7 +4334,7 @@
       <c r="N94" s="17" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="n">
+      <c r="A95" s="13" t="n">
         <v>45782</v>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -4785,7 +4384,7 @@
       <c r="N95" s="17" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="n">
+      <c r="A96" s="13" t="n">
         <v>45783</v>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -4795,47 +4394,27 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F96" s="18" t="n">
-        <v>1.13194</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="n"/>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="14" t="n"/>
       <c r="G96" s="16" t="n"/>
       <c r="H96" s="17" t="n"/>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J96" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K96" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>1.13494</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="15" t="n"/>
+      <c r="K96" s="15" t="n"/>
+      <c r="L96" s="14" t="n"/>
       <c r="M96" s="16" t="n"/>
       <c r="N96" s="17" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="n">
+      <c r="A97" s="13" t="n">
         <v>45784</v>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -4865,7 +4444,7 @@
       <c r="N97" s="17" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="n">
+      <c r="A98" s="13" t="n">
         <v>45785</v>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -4875,47 +4454,37 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F98" s="18" t="n">
-        <v>1.12995</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="n"/>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="14" t="n"/>
       <c r="G98" s="16" t="n"/>
       <c r="H98" s="17" t="n"/>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J98" s="15" t="inlineStr">
         <is>
-          <t>largo</t>
+          <t>corto</t>
         </is>
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L98" s="18" t="n">
-        <v>1.12701</v>
+        <v>1.13202</v>
       </c>
       <c r="M98" s="16" t="n"/>
       <c r="N98" s="17" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="n">
+      <c r="A99" s="13" t="n">
         <v>45786</v>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -4925,22 +4494,12 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F99" s="18" t="n">
-        <v>1.12332</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="n"/>
+      <c r="E99" s="15" t="n"/>
+      <c r="F99" s="14" t="n"/>
       <c r="G99" s="16" t="n"/>
       <c r="H99" s="17" t="n"/>
       <c r="I99" s="14" t="inlineStr">
@@ -4965,7 +4524,7 @@
       <c r="N99" s="17" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="n">
+      <c r="A100" s="13" t="n">
         <v>45789</v>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -4975,22 +4534,12 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F100" s="18" t="n">
-        <v>1.119</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="n"/>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="14" t="n"/>
       <c r="G100" s="16" t="n"/>
       <c r="H100" s="17" t="n"/>
       <c r="I100" s="14" t="inlineStr">
@@ -5005,7 +4554,7 @@
       <c r="N100" s="17" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="n">
+      <c r="A101" s="13" t="n">
         <v>45790</v>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -5015,47 +4564,27 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F101" s="18" t="n">
-        <v>1.11168</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="14" t="n"/>
       <c r="G101" s="16" t="n"/>
       <c r="H101" s="17" t="n"/>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J101" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K101" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L101" s="18" t="n">
-        <v>1.11242</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="15" t="n"/>
+      <c r="K101" s="15" t="n"/>
+      <c r="L101" s="14" t="n"/>
       <c r="M101" s="16" t="n"/>
       <c r="N101" s="17" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="n">
+      <c r="A102" s="13" t="n">
         <v>45791</v>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -5105,7 +4634,7 @@
       <c r="N102" s="17" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="22" t="n">
+      <c r="A103" s="13" t="n">
         <v>45792</v>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -5115,22 +4644,12 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F103" s="18" t="n">
-        <v>1.12012</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="n"/>
+      <c r="E103" s="15" t="n"/>
+      <c r="F103" s="14" t="n"/>
       <c r="G103" s="16" t="n"/>
       <c r="H103" s="17" t="n"/>
       <c r="I103" s="14" t="inlineStr">
@@ -5145,7 +4664,7 @@
       <c r="N103" s="17" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="22" t="n">
+      <c r="A104" s="13" t="n">
         <v>45793</v>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -5155,7 +4674,7 @@
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -5165,7 +4684,7 @@
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
@@ -5175,27 +4694,17 @@
       <c r="H104" s="17" t="n"/>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J104" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K104" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L104" s="18" t="n">
-        <v>1.12195</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J104" s="15" t="n"/>
+      <c r="K104" s="15" t="n"/>
+      <c r="L104" s="14" t="n"/>
       <c r="M104" s="16" t="n"/>
       <c r="N104" s="17" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="22" t="n">
+      <c r="A105" s="13" t="n">
         <v>45796</v>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -5205,22 +4714,12 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F105" s="18" t="n">
-        <v>1.11988</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="n"/>
+      <c r="E105" s="15" t="n"/>
+      <c r="F105" s="14" t="n"/>
       <c r="G105" s="16" t="n"/>
       <c r="H105" s="17" t="n"/>
       <c r="I105" s="14" t="inlineStr">
@@ -5235,7 +4734,7 @@
       <c r="N105" s="17" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="22" t="n">
+      <c r="A106" s="13" t="n">
         <v>45797</v>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -5245,47 +4744,37 @@
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F106" s="18" t="n">
-        <v>1.12512</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="14" t="n"/>
       <c r="G106" s="16" t="n"/>
       <c r="H106" s="17" t="n"/>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J106" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L106" s="18" t="n">
-        <v>1.12778</v>
+        <v>1.12246</v>
       </c>
       <c r="M106" s="16" t="n"/>
       <c r="N106" s="17" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="22" t="n">
+      <c r="A107" s="13" t="n">
         <v>45798</v>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -5325,7 +4814,7 @@
       <c r="N107" s="17" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="22" t="n">
+      <c r="A108" s="13" t="n">
         <v>45799</v>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -5335,22 +4824,12 @@
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F108" s="18" t="n">
-        <v>1.13107</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="14" t="n"/>
       <c r="G108" s="16" t="n"/>
       <c r="H108" s="17" t="n"/>
       <c r="I108" s="14" t="inlineStr">
@@ -5375,7 +4854,7 @@
       <c r="N108" s="17" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="22" t="n">
+      <c r="A109" s="13" t="n">
         <v>45800</v>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -5425,7 +4904,7 @@
       <c r="N109" s="17" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="22" t="n">
+      <c r="A110" s="13" t="n">
         <v>45803</v>
       </c>
       <c r="B110" s="14" t="inlineStr">
@@ -5465,7 +4944,7 @@
       <c r="N110" s="17" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="22" t="n">
+      <c r="A111" s="13" t="n">
         <v>45804</v>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -5475,47 +4954,27 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F111" s="18" t="n">
-        <v>1.13786</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="14" t="n"/>
       <c r="G111" s="16" t="n"/>
       <c r="H111" s="17" t="n"/>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J111" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K111" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L111" s="18" t="n">
-        <v>1.1337</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J111" s="15" t="n"/>
+      <c r="K111" s="15" t="n"/>
+      <c r="L111" s="14" t="n"/>
       <c r="M111" s="16" t="n"/>
       <c r="N111" s="17" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="22" t="n">
+      <c r="A112" s="13" t="n">
         <v>45805</v>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -5555,7 +5014,7 @@
       <c r="N112" s="17" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="22" t="n">
+      <c r="A113" s="13" t="n">
         <v>45806</v>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -5595,7 +5054,7 @@
       <c r="N113" s="17" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="n">
+      <c r="A114" s="13" t="n">
         <v>45807</v>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -5605,22 +5064,12 @@
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F114" s="18" t="n">
-        <v>1.13456</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="n"/>
+      <c r="E114" s="15" t="n"/>
+      <c r="F114" s="14" t="n"/>
       <c r="G114" s="16" t="n"/>
       <c r="H114" s="17" t="n"/>
       <c r="I114" s="14" t="inlineStr">
@@ -5645,7 +5094,7 @@
       <c r="N114" s="17" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="22" t="n">
+      <c r="A115" s="13" t="n">
         <v>45810</v>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -5655,22 +5104,12 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F115" s="18" t="n">
-        <v>1.13819</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="n"/>
+      <c r="E115" s="15" t="n"/>
+      <c r="F115" s="14" t="n"/>
       <c r="G115" s="16" t="n"/>
       <c r="H115" s="17" t="n"/>
       <c r="I115" s="14" t="inlineStr">
@@ -5695,7 +5134,7 @@
       <c r="N115" s="17" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="22" t="n">
+      <c r="A116" s="13" t="n">
         <v>45811</v>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -5745,7 +5184,7 @@
       <c r="N116" s="17" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="22" t="n">
+      <c r="A117" s="13" t="n">
         <v>45812</v>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -5795,7 +5234,7 @@
       <c r="N117" s="17" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="22" t="n">
+      <c r="A118" s="13" t="n">
         <v>45813</v>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -5805,22 +5244,12 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>LR2.1</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="F118" s="18" t="n">
-        <v>1.14045</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="14" t="n"/>
       <c r="G118" s="16" t="n"/>
       <c r="H118" s="17" t="n"/>
       <c r="I118" s="14" t="inlineStr">
@@ -5845,7 +5274,7 @@
       <c r="N118" s="17" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="n">
+      <c r="A119" s="13" t="n">
         <v>45814</v>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -5855,22 +5284,12 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E119" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F119" s="18" t="n">
-        <v>1.14328</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="n"/>
+      <c r="E119" s="15" t="n"/>
+      <c r="F119" s="14" t="n"/>
       <c r="G119" s="16" t="n"/>
       <c r="H119" s="17" t="n"/>
       <c r="I119" s="14" t="inlineStr">
@@ -5885,7 +5304,7 @@
       <c r="N119" s="17" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="22" t="n">
+      <c r="A120" s="13" t="n">
         <v>45817</v>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -5895,22 +5314,12 @@
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F120" s="18" t="n">
-        <v>1.14253</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="14" t="n"/>
       <c r="G120" s="16" t="n"/>
       <c r="H120" s="17" t="n"/>
       <c r="I120" s="14" t="inlineStr">
@@ -5935,7 +5344,7 @@
       <c r="N120" s="17" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="22" t="n">
+      <c r="A121" s="13" t="n">
         <v>45818</v>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -5945,22 +5354,12 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E121" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F121" s="18" t="n">
-        <v>1.13859</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+      <c r="F121" s="14" t="n"/>
       <c r="G121" s="16" t="n"/>
       <c r="H121" s="17" t="n"/>
       <c r="I121" s="14" t="inlineStr">
@@ -5985,7 +5384,7 @@
       <c r="N121" s="17" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="n">
+      <c r="A122" s="13" t="n">
         <v>45819</v>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -6035,7 +5434,7 @@
       <c r="N122" s="17" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="n">
+      <c r="A123" s="13" t="n">
         <v>45820</v>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -6085,7 +5484,7 @@
       <c r="N123" s="17" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="22" t="n">
+      <c r="A124" s="13" t="n">
         <v>45821</v>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -6125,7 +5524,7 @@
       <c r="N124" s="17" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="22" t="n">
+      <c r="A125" s="13" t="n">
         <v>45824</v>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -6135,47 +5534,27 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E125" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F125" s="18" t="n">
-        <v>1.15469</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="n"/>
+      <c r="E125" s="15" t="n"/>
+      <c r="F125" s="14" t="n"/>
       <c r="G125" s="16" t="n"/>
       <c r="H125" s="17" t="n"/>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J125" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K125" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L125" s="18" t="n">
-        <v>1.15865</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="15" t="n"/>
+      <c r="K125" s="15" t="n"/>
+      <c r="L125" s="14" t="n"/>
       <c r="M125" s="16" t="n"/>
       <c r="N125" s="17" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="22" t="n">
+      <c r="A126" s="13" t="n">
         <v>45825</v>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -6215,7 +5594,7 @@
       <c r="N126" s="17" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="22" t="n">
+      <c r="A127" s="13" t="n">
         <v>45826</v>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -6225,47 +5604,27 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D127" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E127" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F127" s="18" t="n">
-        <v>1.15049</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="n"/>
+      <c r="E127" s="15" t="n"/>
+      <c r="F127" s="14" t="n"/>
       <c r="G127" s="16" t="n"/>
       <c r="H127" s="17" t="n"/>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J127" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K127" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L127" s="18" t="n">
-        <v>1.15234</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="15" t="n"/>
+      <c r="K127" s="15" t="n"/>
+      <c r="L127" s="14" t="n"/>
       <c r="M127" s="16" t="n"/>
       <c r="N127" s="17" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="22" t="n">
+      <c r="A128" s="13" t="n">
         <v>45827</v>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -6315,7 +5674,7 @@
       <c r="N128" s="17" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="22" t="n">
+      <c r="A129" s="13" t="n">
         <v>45828</v>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -6365,7 +5724,7 @@
       <c r="N129" s="17" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="22" t="n">
+      <c r="A130" s="13" t="n">
         <v>45831</v>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -6415,7 +5774,7 @@
       <c r="N130" s="17" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="22" t="n">
+      <c r="A131" s="13" t="n">
         <v>45832</v>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -6465,7 +5824,7 @@
       <c r="N131" s="17" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="22" t="n">
+      <c r="A132" s="13" t="n">
         <v>45833</v>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -6475,7 +5834,7 @@
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
@@ -6485,7 +5844,7 @@
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F132" s="18" t="n">
@@ -6495,27 +5854,17 @@
       <c r="H132" s="17" t="n"/>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J132" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K132" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L132" s="18" t="n">
-        <v>1.15898</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="15" t="n"/>
+      <c r="K132" s="15" t="n"/>
+      <c r="L132" s="14" t="n"/>
       <c r="M132" s="16" t="n"/>
       <c r="N132" s="17" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="22" t="n">
+      <c r="A133" s="13" t="n">
         <v>45834</v>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -6525,22 +5874,12 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E133" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F133" s="18" t="n">
-        <v>1.17174</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
+      <c r="F133" s="14" t="n"/>
       <c r="G133" s="16" t="n"/>
       <c r="H133" s="17" t="n"/>
       <c r="I133" s="14" t="inlineStr">
@@ -6555,7 +5894,7 @@
       <c r="N133" s="17" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="22" t="n">
+      <c r="A134" s="13" t="n">
         <v>45835</v>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -6565,47 +5904,27 @@
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E134" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F134" s="18" t="n">
-        <v>1.17093</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="14" t="n"/>
       <c r="G134" s="16" t="n"/>
       <c r="H134" s="17" t="n"/>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J134" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K134" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L134" s="18" t="n">
-        <v>1.17269</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J134" s="15" t="n"/>
+      <c r="K134" s="15" t="n"/>
+      <c r="L134" s="14" t="n"/>
       <c r="M134" s="16" t="n"/>
       <c r="N134" s="17" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="22" t="n">
+      <c r="A135" s="13" t="n">
         <v>45838</v>
       </c>
       <c r="B135" s="14" t="inlineStr">
@@ -6655,7 +5974,7 @@
       <c r="N135" s="17" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="22" t="n">
+      <c r="A136" s="13" t="n">
         <v>45839</v>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -6705,7 +6024,7 @@
       <c r="N136" s="17" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="22" t="n">
+      <c r="A137" s="13" t="n">
         <v>45840</v>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -6715,22 +6034,12 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D137" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E137" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F137" s="18" t="n">
-        <v>1.1788</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="n"/>
+      <c r="E137" s="15" t="n"/>
+      <c r="F137" s="14" t="n"/>
       <c r="G137" s="16" t="n"/>
       <c r="H137" s="17" t="n"/>
       <c r="I137" s="14" t="inlineStr">
@@ -6745,7 +6054,7 @@
       <c r="N137" s="17" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="22" t="n">
+      <c r="A138" s="13" t="n">
         <v>45841</v>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -6785,7 +6094,7 @@
       <c r="N138" s="17" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="22" t="n">
+      <c r="A139" s="13" t="n">
         <v>45842</v>
       </c>
       <c r="B139" s="14" t="inlineStr">
@@ -6795,47 +6104,37 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D139" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E139" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F139" s="18" t="n">
-        <v>1.17725</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="14" t="n"/>
       <c r="G139" s="16" t="n"/>
       <c r="H139" s="17" t="n"/>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J139" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K139" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L139" s="18" t="n">
-        <v>1.17847</v>
+        <v>1.17663</v>
       </c>
       <c r="M139" s="16" t="n"/>
       <c r="N139" s="17" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="22" t="n">
+      <c r="A140" s="13" t="n">
         <v>45845</v>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -6845,22 +6144,12 @@
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E140" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F140" s="18" t="n">
-        <v>1.17644</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="n"/>
+      <c r="E140" s="15" t="n"/>
+      <c r="F140" s="14" t="n"/>
       <c r="G140" s="16" t="n"/>
       <c r="H140" s="17" t="n"/>
       <c r="I140" s="14" t="inlineStr">
@@ -6875,17 +6164,17 @@
       </c>
       <c r="K140" s="15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L140" s="18" t="n">
-        <v>1.17179</v>
+        <v>1.17219</v>
       </c>
       <c r="M140" s="16" t="n"/>
       <c r="N140" s="17" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="22" t="n">
+      <c r="A141" s="13" t="n">
         <v>45846</v>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -6895,22 +6184,12 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E141" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F141" s="18" t="n">
-        <v>1.17487</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+      <c r="F141" s="14" t="n"/>
       <c r="G141" s="16" t="n"/>
       <c r="H141" s="17" t="n"/>
       <c r="I141" s="14" t="inlineStr">
@@ -6925,7 +6204,7 @@
       <c r="N141" s="17" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="22" t="n">
+      <c r="A142" s="13" t="n">
         <v>45847</v>
       </c>
       <c r="B142" s="14" t="inlineStr">
@@ -6965,7 +6244,7 @@
       <c r="N142" s="17" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="22" t="n">
+      <c r="A143" s="13" t="n">
         <v>45848</v>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -6995,7 +6274,7 @@
       <c r="N143" s="17" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="22" t="n">
+      <c r="A144" s="13" t="n">
         <v>45849</v>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -7035,7 +6314,7 @@
       <c r="N144" s="17" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="22" t="n">
+      <c r="A145" s="13" t="n">
         <v>45852</v>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -7065,7 +6344,7 @@
       <c r="N145" s="17" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="22" t="n">
+      <c r="A146" s="13" t="n">
         <v>45853</v>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -7075,22 +6354,12 @@
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F146" s="18" t="n">
-        <v>1.16775</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="14" t="n"/>
       <c r="G146" s="16" t="n"/>
       <c r="H146" s="17" t="n"/>
       <c r="I146" s="14" t="inlineStr">
@@ -7115,7 +6384,7 @@
       <c r="N146" s="17" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="22" t="n">
+      <c r="A147" s="13" t="n">
         <v>45854</v>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -7125,47 +6394,27 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D147" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E147" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F147" s="18" t="n">
-        <v>1.16152</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="n"/>
+      <c r="E147" s="15" t="n"/>
+      <c r="F147" s="14" t="n"/>
       <c r="G147" s="16" t="n"/>
       <c r="H147" s="17" t="n"/>
       <c r="I147" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J147" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K147" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L147" s="18" t="n">
-        <v>1.16281</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J147" s="15" t="n"/>
+      <c r="K147" s="15" t="n"/>
+      <c r="L147" s="14" t="n"/>
       <c r="M147" s="16" t="n"/>
       <c r="N147" s="17" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="22" t="n">
+      <c r="A148" s="13" t="n">
         <v>45855</v>
       </c>
       <c r="B148" s="14" t="inlineStr">
@@ -7175,22 +6424,12 @@
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E148" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F148" s="18" t="n">
-        <v>1.16136</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
+      <c r="F148" s="14" t="n"/>
       <c r="G148" s="16" t="n"/>
       <c r="H148" s="17" t="n"/>
       <c r="I148" s="14" t="inlineStr">
@@ -7215,7 +6454,7 @@
       <c r="N148" s="17" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="22" t="n">
+      <c r="A149" s="13" t="n">
         <v>45856</v>
       </c>
       <c r="B149" s="14" t="inlineStr">
@@ -7225,22 +6464,12 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D149" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E149" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F149" s="18" t="n">
-        <v>1.1634</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
+      <c r="F149" s="14" t="n"/>
       <c r="G149" s="16" t="n"/>
       <c r="H149" s="17" t="n"/>
       <c r="I149" s="14" t="inlineStr">
@@ -7255,7 +6484,7 @@
       <c r="N149" s="17" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="22" t="n">
+      <c r="A150" s="13" t="n">
         <v>45859</v>
       </c>
       <c r="B150" s="14" t="inlineStr">
@@ -7265,22 +6494,12 @@
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F150" s="18" t="n">
-        <v>1.16362</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="n"/>
+      <c r="E150" s="15" t="n"/>
+      <c r="F150" s="14" t="n"/>
       <c r="G150" s="16" t="n"/>
       <c r="H150" s="17" t="n"/>
       <c r="I150" s="14" t="inlineStr">
@@ -7305,7 +6524,7 @@
       <c r="N150" s="17" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="22" t="n">
+      <c r="A151" s="13" t="n">
         <v>45860</v>
       </c>
       <c r="B151" s="14" t="inlineStr">
@@ -7315,27 +6534,17 @@
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D151" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E151" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F151" s="18" t="n">
-        <v>1.16823</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="n"/>
+      <c r="E151" s="15" t="n"/>
+      <c r="F151" s="14" t="n"/>
       <c r="G151" s="16" t="n"/>
       <c r="H151" s="17" t="n"/>
       <c r="I151" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J151" s="15" t="inlineStr">
@@ -7345,17 +6554,17 @@
       </c>
       <c r="K151" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L151" s="18" t="n">
-        <v>1.16815</v>
+        <v>1.16788</v>
       </c>
       <c r="M151" s="16" t="n"/>
       <c r="N151" s="17" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="22" t="n">
+      <c r="A152" s="13" t="n">
         <v>45861</v>
       </c>
       <c r="B152" s="14" t="inlineStr">
@@ -7405,7 +6614,7 @@
       <c r="N152" s="17" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="22" t="n">
+      <c r="A153" s="13" t="n">
         <v>45862</v>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -7415,22 +6624,12 @@
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D153" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E153" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F153" s="18" t="n">
-        <v>1.17621</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n"/>
+      <c r="F153" s="14" t="n"/>
       <c r="G153" s="16" t="n"/>
       <c r="H153" s="17" t="n"/>
       <c r="I153" s="14" t="inlineStr">
@@ -7455,7 +6654,7 @@
       <c r="N153" s="17" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="22" t="n">
+      <c r="A154" s="13" t="n">
         <v>45863</v>
       </c>
       <c r="B154" s="14" t="inlineStr">
@@ -7465,22 +6664,12 @@
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F154" s="18" t="n">
-        <v>1.17585</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="n"/>
+      <c r="E154" s="15" t="n"/>
+      <c r="F154" s="14" t="n"/>
       <c r="G154" s="16" t="n"/>
       <c r="H154" s="17" t="n"/>
       <c r="I154" s="14" t="inlineStr">
@@ -7505,7 +6694,7 @@
       <c r="N154" s="17" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="22" t="n">
+      <c r="A155" s="13" t="n">
         <v>45866</v>
       </c>
       <c r="B155" s="14" t="inlineStr">
@@ -7515,22 +6704,12 @@
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E155" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F155" s="18" t="n">
-        <v>1.17463</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="n"/>
+      <c r="E155" s="15" t="n"/>
+      <c r="F155" s="14" t="n"/>
       <c r="G155" s="16" t="n"/>
       <c r="H155" s="17" t="n"/>
       <c r="I155" s="14" t="inlineStr">
@@ -7545,7 +6724,7 @@
       <c r="N155" s="17" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="22" t="n">
+      <c r="A156" s="13" t="n">
         <v>45867</v>
       </c>
       <c r="B156" s="14" t="inlineStr">
@@ -7555,27 +6734,17 @@
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E156" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F156" s="18" t="n">
-        <v>1.15814</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="n"/>
+      <c r="E156" s="15" t="n"/>
+      <c r="F156" s="14" t="n"/>
       <c r="G156" s="16" t="n"/>
       <c r="H156" s="17" t="n"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J156" s="15" t="inlineStr">
@@ -7585,17 +6754,17 @@
       </c>
       <c r="K156" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L156" s="18" t="n">
-        <v>1.15265</v>
+        <v>1.15188</v>
       </c>
       <c r="M156" s="16" t="n"/>
       <c r="N156" s="17" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="22" t="n">
+      <c r="A157" s="13" t="n">
         <v>45868</v>
       </c>
       <c r="B157" s="14" t="inlineStr">
@@ -7635,7 +6804,7 @@
       <c r="N157" s="17" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="22" t="n">
+      <c r="A158" s="13" t="n">
         <v>45869</v>
       </c>
       <c r="B158" s="14" t="inlineStr">
@@ -7645,47 +6814,27 @@
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F158" s="18" t="n">
-        <v>1.14379</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
+      <c r="F158" s="14" t="n"/>
       <c r="G158" s="16" t="n"/>
       <c r="H158" s="17" t="n"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J158" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K158" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L158" s="18" t="n">
-        <v>1.14606</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J158" s="15" t="n"/>
+      <c r="K158" s="15" t="n"/>
+      <c r="L158" s="14" t="n"/>
       <c r="M158" s="16" t="n"/>
       <c r="N158" s="17" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="22" t="n">
+      <c r="A159" s="13" t="n">
         <v>45870</v>
       </c>
       <c r="B159" s="14" t="inlineStr">
@@ -7735,7 +6884,7 @@
       <c r="N159" s="17" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="22" t="n">
+      <c r="A160" s="13" t="n">
         <v>45873</v>
       </c>
       <c r="B160" s="14" t="inlineStr">
@@ -7745,22 +6894,12 @@
       </c>
       <c r="C160" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E160" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F160" s="18" t="n">
-        <v>1.15501</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="n"/>
+      <c r="E160" s="15" t="n"/>
+      <c r="F160" s="14" t="n"/>
       <c r="G160" s="16" t="n"/>
       <c r="H160" s="17" t="n"/>
       <c r="I160" s="14" t="inlineStr">
@@ -7785,7 +6924,7 @@
       <c r="N160" s="17" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="22" t="n">
+      <c r="A161" s="13" t="n">
         <v>45874</v>
       </c>
       <c r="B161" s="14" t="inlineStr">
@@ -7795,22 +6934,12 @@
       </c>
       <c r="C161" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E161" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F161" s="18" t="n">
-        <v>1.15539</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="15" t="n"/>
+      <c r="F161" s="14" t="n"/>
       <c r="G161" s="16" t="n"/>
       <c r="H161" s="17" t="n"/>
       <c r="I161" s="14" t="inlineStr">
@@ -7825,7 +6954,7 @@
       <c r="N161" s="17" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="22" t="n">
+      <c r="A162" s="13" t="n">
         <v>45875</v>
       </c>
       <c r="B162" s="14" t="inlineStr">
@@ -7855,7 +6984,7 @@
       <c r="N162" s="17" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="22" t="n">
+      <c r="A163" s="13" t="n">
         <v>45876</v>
       </c>
       <c r="B163" s="14" t="inlineStr">
@@ -7865,22 +6994,12 @@
       </c>
       <c r="C163" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D163" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E163" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F163" s="18" t="n">
-        <v>1.16658</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="15" t="n"/>
+      <c r="F163" s="14" t="n"/>
       <c r="G163" s="16" t="n"/>
       <c r="H163" s="17" t="n"/>
       <c r="I163" s="14" t="inlineStr">
@@ -7895,7 +7014,7 @@
       <c r="N163" s="17" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="22" t="n">
+      <c r="A164" s="13" t="n">
         <v>45877</v>
       </c>
       <c r="B164" s="14" t="inlineStr">
@@ -7905,22 +7024,12 @@
       </c>
       <c r="C164" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E164" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F164" s="18" t="n">
-        <v>1.16548</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="n"/>
+      <c r="E164" s="15" t="n"/>
+      <c r="F164" s="14" t="n"/>
       <c r="G164" s="16" t="n"/>
       <c r="H164" s="17" t="n"/>
       <c r="I164" s="14" t="inlineStr">
@@ -7935,7 +7044,7 @@
       <c r="N164" s="17" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="22" t="n">
+      <c r="A165" s="13" t="n">
         <v>45880</v>
       </c>
       <c r="B165" s="14" t="inlineStr">
@@ -7965,7 +7074,7 @@
       <c r="N165" s="17" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="22" t="n">
+      <c r="A166" s="13" t="n">
         <v>45881</v>
       </c>
       <c r="B166" s="14" t="inlineStr">
@@ -8015,7 +7124,7 @@
       <c r="N166" s="17" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="22" t="n">
+      <c r="A167" s="13" t="n">
         <v>45882</v>
       </c>
       <c r="B167" s="14" t="inlineStr">
@@ -8025,22 +7134,12 @@
       </c>
       <c r="C167" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D167" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E167" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F167" s="18" t="n">
-        <v>1.16875</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="n"/>
+      <c r="E167" s="15" t="n"/>
+      <c r="F167" s="14" t="n"/>
       <c r="G167" s="16" t="n"/>
       <c r="H167" s="17" t="n"/>
       <c r="I167" s="14" t="inlineStr">
@@ -8055,7 +7154,7 @@
       <c r="N167" s="17" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="22" t="n">
+      <c r="A168" s="13" t="n">
         <v>45883</v>
       </c>
       <c r="B168" s="14" t="inlineStr">
@@ -8065,47 +7164,27 @@
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D168" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E168" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F168" s="18" t="n">
-        <v>1.16988</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="15" t="n"/>
+      <c r="F168" s="14" t="n"/>
       <c r="G168" s="16" t="n"/>
       <c r="H168" s="17" t="n"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J168" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K168" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L168" s="18" t="n">
-        <v>1.16678</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J168" s="15" t="n"/>
+      <c r="K168" s="15" t="n"/>
+      <c r="L168" s="14" t="n"/>
       <c r="M168" s="16" t="n"/>
       <c r="N168" s="17" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="22" t="n">
+      <c r="A169" s="13" t="n">
         <v>45884</v>
       </c>
       <c r="B169" s="14" t="inlineStr">
@@ -8115,22 +7194,12 @@
       </c>
       <c r="C169" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D169" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E169" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F169" s="18" t="n">
-        <v>1.16644</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D169" s="15" t="n"/>
+      <c r="E169" s="15" t="n"/>
+      <c r="F169" s="14" t="n"/>
       <c r="G169" s="16" t="n"/>
       <c r="H169" s="17" t="n"/>
       <c r="I169" s="14" t="inlineStr">
@@ -8145,7 +7214,7 @@
       <c r="N169" s="17" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="22" t="n">
+      <c r="A170" s="13" t="n">
         <v>45887</v>
       </c>
       <c r="B170" s="14" t="inlineStr">
@@ -8155,27 +7224,17 @@
       </c>
       <c r="C170" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E170" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F170" s="18" t="n">
-        <v>1.16935</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D170" s="15" t="n"/>
+      <c r="E170" s="15" t="n"/>
+      <c r="F170" s="14" t="n"/>
       <c r="G170" s="16" t="n"/>
       <c r="H170" s="17" t="n"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J170" s="15" t="inlineStr">
@@ -8185,17 +7244,17 @@
       </c>
       <c r="K170" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L170" s="18" t="n">
-        <v>1.1671</v>
+        <v>1.16662</v>
       </c>
       <c r="M170" s="16" t="n"/>
       <c r="N170" s="17" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="22" t="n">
+      <c r="A171" s="13" t="n">
         <v>45888</v>
       </c>
       <c r="B171" s="14" t="inlineStr">
@@ -8205,22 +7264,12 @@
       </c>
       <c r="C171" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D171" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E171" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F171" s="18" t="n">
-        <v>1.16746</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D171" s="15" t="n"/>
+      <c r="E171" s="15" t="n"/>
+      <c r="F171" s="14" t="n"/>
       <c r="G171" s="16" t="n"/>
       <c r="H171" s="17" t="n"/>
       <c r="I171" s="14" t="inlineStr">
@@ -8235,7 +7284,7 @@
       <c r="N171" s="17" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="22" t="n">
+      <c r="A172" s="13" t="n">
         <v>45889</v>
       </c>
       <c r="B172" s="14" t="inlineStr">
@@ -8275,7 +7324,7 @@
       <c r="N172" s="17" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="22" t="n">
+      <c r="A173" s="13" t="n">
         <v>45890</v>
       </c>
       <c r="B173" s="14" t="inlineStr">
@@ -8285,21 +7334,21 @@
       </c>
       <c r="C173" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR1</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="E173" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F173" s="18" t="n">
-        <v>1.16551</v>
+        <v>1.16409</v>
       </c>
       <c r="G173" s="16" t="n"/>
       <c r="H173" s="17" t="n"/>
@@ -8325,7 +7374,7 @@
       <c r="N173" s="17" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="22" t="n">
+      <c r="A174" s="13" t="n">
         <v>45891</v>
       </c>
       <c r="B174" s="14" t="inlineStr">
@@ -8375,7 +7424,7 @@
       <c r="N174" s="17" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="22" t="n">
+      <c r="A175" s="13" t="n">
         <v>45894</v>
       </c>
       <c r="B175" s="14" t="inlineStr">
@@ -8415,7 +7464,7 @@
       <c r="N175" s="17" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="22" t="n">
+      <c r="A176" s="13" t="n">
         <v>45895</v>
       </c>
       <c r="B176" s="14" t="inlineStr">
@@ -8425,22 +7474,12 @@
       </c>
       <c r="C176" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E176" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F176" s="18" t="n">
-        <v>1.161</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D176" s="15" t="n"/>
+      <c r="E176" s="15" t="n"/>
+      <c r="F176" s="14" t="n"/>
       <c r="G176" s="16" t="n"/>
       <c r="H176" s="17" t="n"/>
       <c r="I176" s="14" t="inlineStr">
@@ -8455,7 +7494,7 @@
       <c r="N176" s="17" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="22" t="n">
+      <c r="A177" s="13" t="n">
         <v>45896</v>
       </c>
       <c r="B177" s="14" t="inlineStr">
@@ -8465,22 +7504,12 @@
       </c>
       <c r="C177" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D177" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E177" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F177" s="18" t="n">
-        <v>1.16215</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D177" s="15" t="n"/>
+      <c r="E177" s="15" t="n"/>
+      <c r="F177" s="14" t="n"/>
       <c r="G177" s="16" t="n"/>
       <c r="H177" s="17" t="n"/>
       <c r="I177" s="14" t="inlineStr">
@@ -8495,7 +7524,7 @@
       <c r="N177" s="17" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="22" t="n">
+      <c r="A178" s="13" t="n">
         <v>45897</v>
       </c>
       <c r="B178" s="14" t="inlineStr">
@@ -8505,22 +7534,12 @@
       </c>
       <c r="C178" s="14" t="inlineStr">
         <is>
-          <t>LR2.2</t>
-        </is>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E178" s="15" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F178" s="18" t="n">
-        <v>1.16321</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D178" s="15" t="n"/>
+      <c r="E178" s="15" t="n"/>
+      <c r="F178" s="14" t="n"/>
       <c r="G178" s="16" t="n"/>
       <c r="H178" s="17" t="n"/>
       <c r="I178" s="14" t="inlineStr">
@@ -8545,7 +7564,7 @@
       <c r="N178" s="17" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="22" t="n">
+      <c r="A179" s="13" t="n">
         <v>45898</v>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -8565,7 +7584,7 @@
       </c>
       <c r="E179" s="15" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F179" s="18" t="n">
@@ -8595,7 +7614,7 @@
       <c r="N179" s="17" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="22" t="n">
+      <c r="A180" s="13" t="n">
         <v>45901</v>
       </c>
       <c r="B180" s="14" t="inlineStr">
@@ -8605,22 +7624,12 @@
       </c>
       <c r="C180" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E180" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F180" s="18" t="n">
-        <v>1.17142</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D180" s="15" t="n"/>
+      <c r="E180" s="15" t="n"/>
+      <c r="F180" s="14" t="n"/>
       <c r="G180" s="16" t="n"/>
       <c r="H180" s="17" t="n"/>
       <c r="I180" s="14" t="inlineStr">
@@ -8635,7 +7644,7 @@
       <c r="N180" s="17" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="22" t="n">
+      <c r="A181" s="13" t="n">
         <v>45902</v>
       </c>
       <c r="B181" s="14" t="inlineStr">
@@ -8685,7 +7694,7 @@
       <c r="N181" s="17" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="22" t="n">
+      <c r="A182" s="13" t="n">
         <v>45903</v>
       </c>
       <c r="B182" s="14" t="inlineStr">
@@ -8695,7 +7704,7 @@
       </c>
       <c r="C182" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>LR1</t>
         </is>
       </c>
       <c r="D182" s="15" t="inlineStr">
@@ -8705,22 +7714,22 @@
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F182" s="18" t="n">
-        <v>1.16284</v>
+        <v>1.1623</v>
       </c>
       <c r="G182" s="16" t="n"/>
       <c r="H182" s="17" t="n"/>
       <c r="I182" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
+          <t>NYC1</t>
         </is>
       </c>
       <c r="J182" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K182" s="15" t="inlineStr">
@@ -8729,13 +7738,13 @@
         </is>
       </c>
       <c r="L182" s="18" t="n">
-        <v>1.16542</v>
+        <v>1.16081</v>
       </c>
       <c r="M182" s="16" t="n"/>
       <c r="N182" s="17" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="22" t="n">
+      <c r="A183" s="13" t="n">
         <v>45904</v>
       </c>
       <c r="B183" s="14" t="inlineStr">
@@ -8745,7 +7754,7 @@
       </c>
       <c r="C183" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D183" s="15" t="inlineStr">
@@ -8755,7 +7764,7 @@
       </c>
       <c r="E183" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F183" s="18" t="n">
@@ -8785,7 +7794,7 @@
       <c r="N183" s="17" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="22" t="n">
+      <c r="A184" s="13" t="n">
         <v>45905</v>
       </c>
       <c r="B184" s="14" t="inlineStr">
@@ -8825,7 +7834,7 @@
       <c r="N184" s="17" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="22" t="n">
+      <c r="A185" s="13" t="n">
         <v>45908</v>
       </c>
       <c r="B185" s="14" t="inlineStr">
@@ -8835,47 +7844,27 @@
       </c>
       <c r="C185" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D185" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E185" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F185" s="18" t="n">
-        <v>1.17197</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D185" s="15" t="n"/>
+      <c r="E185" s="15" t="n"/>
+      <c r="F185" s="14" t="n"/>
       <c r="G185" s="16" t="n"/>
       <c r="H185" s="17" t="n"/>
       <c r="I185" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J185" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K185" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L185" s="18" t="n">
-        <v>1.17427</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J185" s="15" t="n"/>
+      <c r="K185" s="15" t="n"/>
+      <c r="L185" s="14" t="n"/>
       <c r="M185" s="16" t="n"/>
       <c r="N185" s="17" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="22" t="n">
+      <c r="A186" s="13" t="n">
         <v>45909</v>
       </c>
       <c r="B186" s="14" t="inlineStr">
@@ -8925,7 +7914,7 @@
       <c r="N186" s="17" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="22" t="n">
+      <c r="A187" s="13" t="n">
         <v>45910</v>
       </c>
       <c r="B187" s="14" t="inlineStr">
@@ -8975,7 +7964,7 @@
       <c r="N187" s="17" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="22" t="n">
+      <c r="A188" s="13" t="n">
         <v>45911</v>
       </c>
       <c r="B188" s="14" t="inlineStr">
@@ -8985,22 +7974,12 @@
       </c>
       <c r="C188" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E188" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F188" s="18" t="n">
-        <v>1.16927</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D188" s="15" t="n"/>
+      <c r="E188" s="15" t="n"/>
+      <c r="F188" s="14" t="n"/>
       <c r="G188" s="16" t="n"/>
       <c r="H188" s="17" t="n"/>
       <c r="I188" s="14" t="inlineStr">
@@ -9025,7 +8004,7 @@
       <c r="N188" s="17" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="22" t="n">
+      <c r="A189" s="13" t="n">
         <v>45912</v>
       </c>
       <c r="B189" s="14" t="inlineStr">
@@ -9055,27 +8034,17 @@
       <c r="H189" s="17" t="n"/>
       <c r="I189" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
-        </is>
-      </c>
-      <c r="J189" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K189" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L189" s="18" t="n">
-        <v>1.17204</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J189" s="15" t="n"/>
+      <c r="K189" s="15" t="n"/>
+      <c r="L189" s="14" t="n"/>
       <c r="M189" s="16" t="n"/>
       <c r="N189" s="17" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="22" t="n">
+      <c r="A190" s="13" t="n">
         <v>45915</v>
       </c>
       <c r="B190" s="14" t="inlineStr">
@@ -9085,22 +8054,12 @@
       </c>
       <c r="C190" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D190" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E190" s="15" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="F190" s="18" t="n">
-        <v>1.17298</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" s="15" t="n"/>
+      <c r="E190" s="15" t="n"/>
+      <c r="F190" s="14" t="n"/>
       <c r="G190" s="16" t="n"/>
       <c r="H190" s="17" t="n"/>
       <c r="I190" s="14" t="inlineStr">
@@ -9125,7 +8084,7 @@
       <c r="N190" s="17" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="22" t="n">
+      <c r="A191" s="13" t="n">
         <v>45916</v>
       </c>
       <c r="B191" s="14" t="inlineStr">
@@ -9135,22 +8094,12 @@
       </c>
       <c r="C191" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D191" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E191" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F191" s="18" t="n">
-        <v>1.17866</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="n"/>
+      <c r="E191" s="15" t="n"/>
+      <c r="F191" s="14" t="n"/>
       <c r="G191" s="16" t="n"/>
       <c r="H191" s="17" t="n"/>
       <c r="I191" s="14" t="inlineStr">
@@ -9165,7 +8114,7 @@
       <c r="N191" s="17" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="22" t="n">
+      <c r="A192" s="13" t="n">
         <v>45917</v>
       </c>
       <c r="B192" s="14" t="inlineStr">
@@ -9175,22 +8124,12 @@
       </c>
       <c r="C192" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D192" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E192" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F192" s="18" t="n">
-        <v>1.18511</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="n"/>
+      <c r="E192" s="15" t="n"/>
+      <c r="F192" s="14" t="n"/>
       <c r="G192" s="16" t="n"/>
       <c r="H192" s="17" t="n"/>
       <c r="I192" s="14" t="inlineStr">
@@ -9205,7 +8144,7 @@
       <c r="N192" s="17" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="22" t="n">
+      <c r="A193" s="13" t="n">
         <v>45918</v>
       </c>
       <c r="B193" s="14" t="inlineStr">
@@ -9215,21 +8154,21 @@
       </c>
       <c r="C193" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR1</t>
         </is>
       </c>
       <c r="D193" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="E193" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F193" s="18" t="n">
-        <v>1.18287</v>
+        <v>1.18074</v>
       </c>
       <c r="G193" s="16" t="n"/>
       <c r="H193" s="17" t="n"/>
@@ -9255,7 +8194,7 @@
       <c r="N193" s="17" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="22" t="n">
+      <c r="A194" s="13" t="n">
         <v>45919</v>
       </c>
       <c r="B194" s="14" t="inlineStr">
@@ -9265,22 +8204,12 @@
       </c>
       <c r="C194" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E194" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F194" s="18" t="n">
-        <v>1.17719</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="n"/>
+      <c r="E194" s="15" t="n"/>
+      <c r="F194" s="14" t="n"/>
       <c r="G194" s="16" t="n"/>
       <c r="H194" s="17" t="n"/>
       <c r="I194" s="14" t="inlineStr">
@@ -9305,7 +8234,7 @@
       <c r="N194" s="17" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="22" t="n">
+      <c r="A195" s="13" t="n">
         <v>45922</v>
       </c>
       <c r="B195" s="14" t="inlineStr">
@@ -9315,22 +8244,12 @@
       </c>
       <c r="C195" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D195" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E195" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F195" s="18" t="n">
-        <v>1.17477</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="n"/>
+      <c r="E195" s="15" t="n"/>
+      <c r="F195" s="14" t="n"/>
       <c r="G195" s="16" t="n"/>
       <c r="H195" s="17" t="n"/>
       <c r="I195" s="14" t="inlineStr">
@@ -9345,17 +8264,17 @@
       </c>
       <c r="K195" s="15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L195" s="18" t="n">
-        <v>1.17873</v>
+        <v>1.17877</v>
       </c>
       <c r="M195" s="16" t="n"/>
       <c r="N195" s="17" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="22" t="n">
+      <c r="A196" s="13" t="n">
         <v>45923</v>
       </c>
       <c r="B196" s="14" t="inlineStr">
@@ -9365,7 +8284,7 @@
       </c>
       <c r="C196" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D196" s="15" t="inlineStr">
@@ -9375,7 +8294,7 @@
       </c>
       <c r="E196" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F196" s="18" t="n">
@@ -9385,27 +8304,17 @@
       <c r="H196" s="17" t="n"/>
       <c r="I196" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J196" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K196" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L196" s="18" t="n">
-        <v>1.17787</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J196" s="15" t="n"/>
+      <c r="K196" s="15" t="n"/>
+      <c r="L196" s="14" t="n"/>
       <c r="M196" s="16" t="n"/>
       <c r="N196" s="17" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="22" t="n">
+      <c r="A197" s="13" t="n">
         <v>45924</v>
       </c>
       <c r="B197" s="14" t="inlineStr">
@@ -9415,22 +8324,12 @@
       </c>
       <c r="C197" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D197" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E197" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F197" s="18" t="n">
-        <v>1.17947</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D197" s="15" t="n"/>
+      <c r="E197" s="15" t="n"/>
+      <c r="F197" s="14" t="n"/>
       <c r="G197" s="16" t="n"/>
       <c r="H197" s="17" t="n"/>
       <c r="I197" s="14" t="inlineStr">
@@ -9445,7 +8344,7 @@
       <c r="N197" s="17" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="22" t="n">
+      <c r="A198" s="13" t="n">
         <v>45925</v>
       </c>
       <c r="B198" s="14" t="inlineStr">
@@ -9455,7 +8354,7 @@
       </c>
       <c r="C198" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D198" s="15" t="inlineStr">
@@ -9465,7 +8364,7 @@
       </c>
       <c r="E198" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F198" s="18" t="n">
@@ -9495,7 +8394,7 @@
       <c r="N198" s="17" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="22" t="n">
+      <c r="A199" s="13" t="n">
         <v>45926</v>
       </c>
       <c r="B199" s="14" t="inlineStr">
@@ -9545,7 +8444,7 @@
       <c r="N199" s="17" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="22" t="n">
+      <c r="A200" s="13" t="n">
         <v>45929</v>
       </c>
       <c r="B200" s="14" t="inlineStr">
@@ -9575,27 +8474,17 @@
       <c r="H200" s="17" t="n"/>
       <c r="I200" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J200" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K200" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L200" s="18" t="n">
-        <v>1.17329</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J200" s="15" t="n"/>
+      <c r="K200" s="15" t="n"/>
+      <c r="L200" s="14" t="n"/>
       <c r="M200" s="16" t="n"/>
       <c r="N200" s="17" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="22" t="n">
+      <c r="A201" s="13" t="n">
         <v>45930</v>
       </c>
       <c r="B201" s="14" t="inlineStr">
@@ -9605,22 +8494,12 @@
       </c>
       <c r="C201" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D201" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E201" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F201" s="18" t="n">
-        <v>1.17322</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="n"/>
+      <c r="E201" s="15" t="n"/>
+      <c r="F201" s="14" t="n"/>
       <c r="G201" s="16" t="n"/>
       <c r="H201" s="17" t="n"/>
       <c r="I201" s="14" t="inlineStr">
@@ -9635,7 +8514,7 @@
       <c r="N201" s="17" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="22" t="n">
+      <c r="A202" s="13" t="n">
         <v>45931</v>
       </c>
       <c r="B202" s="14" t="inlineStr">
@@ -9645,22 +8524,12 @@
       </c>
       <c r="C202" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E202" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F202" s="18" t="n">
-        <v>1.17424</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="15" t="n"/>
+      <c r="E202" s="15" t="n"/>
+      <c r="F202" s="14" t="n"/>
       <c r="G202" s="16" t="n"/>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="14" t="inlineStr">
@@ -9685,7 +8554,7 @@
       <c r="N202" s="17" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="22" t="n">
+      <c r="A203" s="13" t="n">
         <v>45932</v>
       </c>
       <c r="B203" s="14" t="inlineStr">
@@ -9695,22 +8564,12 @@
       </c>
       <c r="C203" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D203" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E203" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F203" s="18" t="n">
-        <v>1.17418</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="n"/>
+      <c r="E203" s="15" t="n"/>
+      <c r="F203" s="14" t="n"/>
       <c r="G203" s="16" t="n"/>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="14" t="inlineStr">
@@ -9735,7 +8594,7 @@
       <c r="N203" s="17" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="22" t="n">
+      <c r="A204" s="13" t="n">
         <v>45933</v>
       </c>
       <c r="B204" s="14" t="inlineStr">
@@ -9745,22 +8604,12 @@
       </c>
       <c r="C204" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D204" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E204" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F204" s="18" t="n">
-        <v>1.17292</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" s="15" t="n"/>
+      <c r="E204" s="15" t="n"/>
+      <c r="F204" s="14" t="n"/>
       <c r="G204" s="16" t="n"/>
       <c r="H204" s="17" t="n"/>
       <c r="I204" s="14" t="inlineStr">
@@ -9775,7 +8624,7 @@
       <c r="N204" s="17" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="22" t="n">
+      <c r="A205" s="13" t="n">
         <v>45936</v>
       </c>
       <c r="B205" s="14" t="inlineStr">
@@ -9785,47 +8634,27 @@
       </c>
       <c r="C205" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D205" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E205" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F205" s="18" t="n">
-        <v>1.1706</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D205" s="15" t="n"/>
+      <c r="E205" s="15" t="n"/>
+      <c r="F205" s="14" t="n"/>
       <c r="G205" s="16" t="n"/>
       <c r="H205" s="17" t="n"/>
       <c r="I205" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J205" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K205" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L205" s="18" t="n">
-        <v>1.16516</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J205" s="15" t="n"/>
+      <c r="K205" s="15" t="n"/>
+      <c r="L205" s="14" t="n"/>
       <c r="M205" s="16" t="n"/>
       <c r="N205" s="17" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="22" t="n">
+      <c r="A206" s="13" t="n">
         <v>45937</v>
       </c>
       <c r="B206" s="14" t="inlineStr">
@@ -9835,22 +8664,12 @@
       </c>
       <c r="C206" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D206" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E206" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F206" s="18" t="n">
-        <v>1.16963</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="n"/>
+      <c r="E206" s="15" t="n"/>
+      <c r="F206" s="14" t="n"/>
       <c r="G206" s="16" t="n"/>
       <c r="H206" s="17" t="n"/>
       <c r="I206" s="14" t="inlineStr">
@@ -9865,7 +8684,7 @@
       <c r="N206" s="17" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="22" t="n">
+      <c r="A207" s="13" t="n">
         <v>45938</v>
       </c>
       <c r="B207" s="14" t="inlineStr">
@@ -9895,27 +8714,27 @@
       <c r="H207" s="17" t="n"/>
       <c r="I207" s="14" t="inlineStr">
         <is>
-          <t>NYR2</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J207" s="15" t="inlineStr">
         <is>
-          <t>largo</t>
+          <t>corto</t>
         </is>
       </c>
       <c r="K207" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L207" s="18" t="n">
-        <v>1.16251</v>
+        <v>1.16378</v>
       </c>
       <c r="M207" s="16" t="n"/>
       <c r="N207" s="17" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="22" t="n">
+      <c r="A208" s="13" t="n">
         <v>45939</v>
       </c>
       <c r="B208" s="14" t="inlineStr">
@@ -9965,7 +8784,7 @@
       <c r="N208" s="17" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="22" t="n">
+      <c r="A209" s="13" t="n">
         <v>45940</v>
       </c>
       <c r="B209" s="14" t="inlineStr">
@@ -9975,22 +8794,12 @@
       </c>
       <c r="C209" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D209" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E209" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F209" s="18" t="n">
-        <v>1.1574</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D209" s="15" t="n"/>
+      <c r="E209" s="15" t="n"/>
+      <c r="F209" s="14" t="n"/>
       <c r="G209" s="16" t="n"/>
       <c r="H209" s="17" t="n"/>
       <c r="I209" s="14" t="inlineStr">
@@ -10015,7 +8824,7 @@
       <c r="N209" s="17" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="22" t="n">
+      <c r="A210" s="13" t="n">
         <v>45943</v>
       </c>
       <c r="B210" s="14" t="inlineStr">
@@ -10065,7 +8874,7 @@
       <c r="N210" s="17" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="22" t="n">
+      <c r="A211" s="13" t="n">
         <v>45944</v>
       </c>
       <c r="B211" s="14" t="inlineStr">
@@ -10105,7 +8914,7 @@
       <c r="N211" s="17" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="22" t="n">
+      <c r="A212" s="13" t="n">
         <v>45945</v>
       </c>
       <c r="B212" s="14" t="inlineStr">
@@ -10115,47 +8924,37 @@
       </c>
       <c r="C212" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D212" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E212" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F212" s="18" t="n">
-        <v>1.16258</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D212" s="15" t="n"/>
+      <c r="E212" s="15" t="n"/>
+      <c r="F212" s="14" t="n"/>
       <c r="G212" s="16" t="n"/>
       <c r="H212" s="17" t="n"/>
       <c r="I212" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J212" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="K212" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L212" s="18" t="n">
-        <v>1.16453</v>
+        <v>1.16103</v>
       </c>
       <c r="M212" s="16" t="n"/>
       <c r="N212" s="17" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="22" t="n">
+      <c r="A213" s="13" t="n">
         <v>45946</v>
       </c>
       <c r="B213" s="14" t="inlineStr">
@@ -10185,7 +8984,7 @@
       <c r="N213" s="17" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="22" t="n">
+      <c r="A214" s="13" t="n">
         <v>45947</v>
       </c>
       <c r="B214" s="14" t="inlineStr">
@@ -10235,7 +9034,7 @@
       <c r="N214" s="17" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="22" t="n">
+      <c r="A215" s="13" t="n">
         <v>45950</v>
       </c>
       <c r="B215" s="14" t="inlineStr">
@@ -10285,7 +9084,7 @@
       <c r="N215" s="17" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="22" t="n">
+      <c r="A216" s="13" t="n">
         <v>45951</v>
       </c>
       <c r="B216" s="14" t="inlineStr">
@@ -10295,22 +9094,12 @@
       </c>
       <c r="C216" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D216" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E216" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F216" s="18" t="n">
-        <v>1.16326</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D216" s="15" t="n"/>
+      <c r="E216" s="15" t="n"/>
+      <c r="F216" s="14" t="n"/>
       <c r="G216" s="16" t="n"/>
       <c r="H216" s="17" t="n"/>
       <c r="I216" s="14" t="inlineStr">
@@ -10335,7 +9124,7 @@
       <c r="N216" s="17" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="22" t="n">
+      <c r="A217" s="13" t="n">
         <v>45952</v>
       </c>
       <c r="B217" s="14" t="inlineStr">
@@ -10385,7 +9174,7 @@
       <c r="N217" s="17" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="22" t="n">
+      <c r="A218" s="13" t="n">
         <v>45953</v>
       </c>
       <c r="B218" s="14" t="inlineStr">
@@ -10425,7 +9214,7 @@
       <c r="N218" s="17" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="22" t="n">
+      <c r="A219" s="13" t="n">
         <v>45954</v>
       </c>
       <c r="B219" s="14" t="inlineStr">
@@ -10475,7 +9264,7 @@
       <c r="N219" s="17" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="22" t="n">
+      <c r="A220" s="13" t="n">
         <v>45957</v>
       </c>
       <c r="B220" s="14" t="inlineStr">
@@ -10525,7 +9314,7 @@
       <c r="N220" s="17" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="22" t="n">
+      <c r="A221" s="13" t="n">
         <v>45958</v>
       </c>
       <c r="B221" s="14" t="inlineStr">
@@ -10575,7 +9364,7 @@
       <c r="N221" s="17" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="22" t="n">
+      <c r="A222" s="13" t="n">
         <v>45959</v>
       </c>
       <c r="B222" s="14" t="inlineStr">
@@ -10625,7 +9414,7 @@
       <c r="N222" s="17" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="22" t="n">
+      <c r="A223" s="13" t="n">
         <v>45960</v>
       </c>
       <c r="B223" s="14" t="inlineStr">
@@ -10665,7 +9454,7 @@
       <c r="N223" s="17" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="22" t="n">
+      <c r="A224" s="13" t="n">
         <v>45961</v>
       </c>
       <c r="B224" s="14" t="inlineStr">
@@ -10705,7 +9494,7 @@
       <c r="N224" s="17" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="22" t="n">
+      <c r="A225" s="13" t="n">
         <v>45964</v>
       </c>
       <c r="B225" s="14" t="inlineStr">
@@ -10755,7 +9544,7 @@
       <c r="N225" s="17" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="22" t="n">
+      <c r="A226" s="13" t="n">
         <v>45965</v>
       </c>
       <c r="B226" s="14" t="inlineStr">
@@ -10805,7 +9594,7 @@
       <c r="N226" s="17" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="22" t="n">
+      <c r="A227" s="13" t="n">
         <v>45966</v>
       </c>
       <c r="B227" s="14" t="inlineStr">
@@ -10845,7 +9634,7 @@
       <c r="N227" s="17" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="22" t="n">
+      <c r="A228" s="13" t="n">
         <v>45967</v>
       </c>
       <c r="B228" s="14" t="inlineStr">
@@ -10855,22 +9644,12 @@
       </c>
       <c r="C228" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D228" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E228" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F228" s="18" t="n">
-        <v>1.15089</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D228" s="15" t="n"/>
+      <c r="E228" s="15" t="n"/>
+      <c r="F228" s="14" t="n"/>
       <c r="G228" s="16" t="n"/>
       <c r="H228" s="17" t="n"/>
       <c r="I228" s="14" t="inlineStr">
@@ -10895,7 +9674,7 @@
       <c r="N228" s="17" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="22" t="n">
+      <c r="A229" s="13" t="n">
         <v>45968</v>
       </c>
       <c r="B229" s="14" t="inlineStr">
@@ -10905,47 +9684,27 @@
       </c>
       <c r="C229" s="14" t="inlineStr">
         <is>
-          <t>LR2.1</t>
-        </is>
-      </c>
-      <c r="D229" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E229" s="15" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="F229" s="18" t="n">
-        <v>1.15294</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D229" s="15" t="n"/>
+      <c r="E229" s="15" t="n"/>
+      <c r="F229" s="14" t="n"/>
       <c r="G229" s="16" t="n"/>
       <c r="H229" s="17" t="n"/>
       <c r="I229" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J229" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K229" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L229" s="18" t="n">
-        <v>1.15294</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J229" s="15" t="n"/>
+      <c r="K229" s="15" t="n"/>
+      <c r="L229" s="14" t="n"/>
       <c r="M229" s="16" t="n"/>
       <c r="N229" s="17" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="22" t="n">
+      <c r="A230" s="13" t="n">
         <v>45971</v>
       </c>
       <c r="B230" s="14" t="inlineStr">
@@ -10955,47 +9714,27 @@
       </c>
       <c r="C230" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D230" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E230" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F230" s="18" t="n">
-        <v>1.15624</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D230" s="15" t="n"/>
+      <c r="E230" s="15" t="n"/>
+      <c r="F230" s="14" t="n"/>
       <c r="G230" s="16" t="n"/>
       <c r="H230" s="17" t="n"/>
       <c r="I230" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J230" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K230" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L230" s="18" t="n">
-        <v>1.15829</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J230" s="15" t="n"/>
+      <c r="K230" s="15" t="n"/>
+      <c r="L230" s="14" t="n"/>
       <c r="M230" s="16" t="n"/>
       <c r="N230" s="17" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="22" t="n">
+      <c r="A231" s="13" t="n">
         <v>45972</v>
       </c>
       <c r="B231" s="14" t="inlineStr">
@@ -11035,7 +9774,7 @@
       <c r="N231" s="17" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="22" t="n">
+      <c r="A232" s="13" t="n">
         <v>45973</v>
       </c>
       <c r="B232" s="14" t="inlineStr">
@@ -11085,7 +9824,7 @@
       <c r="N232" s="17" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="22" t="n">
+      <c r="A233" s="13" t="n">
         <v>45974</v>
       </c>
       <c r="B233" s="14" t="inlineStr">
@@ -11095,47 +9834,27 @@
       </c>
       <c r="C233" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D233" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E233" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F233" s="18" t="n">
-        <v>1.15945</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D233" s="15" t="n"/>
+      <c r="E233" s="15" t="n"/>
+      <c r="F233" s="14" t="n"/>
       <c r="G233" s="16" t="n"/>
       <c r="H233" s="17" t="n"/>
       <c r="I233" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J233" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K233" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L233" s="18" t="n">
-        <v>1.16347</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J233" s="15" t="n"/>
+      <c r="K233" s="15" t="n"/>
+      <c r="L233" s="14" t="n"/>
       <c r="M233" s="16" t="n"/>
       <c r="N233" s="17" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="22" t="n">
+      <c r="A234" s="13" t="n">
         <v>45975</v>
       </c>
       <c r="B234" s="14" t="inlineStr">
@@ -11185,7 +9904,7 @@
       <c r="N234" s="17" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="22" t="n">
+      <c r="A235" s="13" t="n">
         <v>45978</v>
       </c>
       <c r="B235" s="14" t="inlineStr">
@@ -11225,7 +9944,7 @@
       <c r="N235" s="17" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="22" t="n">
+      <c r="A236" s="13" t="n">
         <v>45979</v>
       </c>
       <c r="B236" s="14" t="inlineStr">
@@ -11235,22 +9954,12 @@
       </c>
       <c r="C236" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E236" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F236" s="18" t="n">
-        <v>1.16036</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D236" s="15" t="n"/>
+      <c r="E236" s="15" t="n"/>
+      <c r="F236" s="14" t="n"/>
       <c r="G236" s="16" t="n"/>
       <c r="H236" s="17" t="n"/>
       <c r="I236" s="14" t="inlineStr">
@@ -11275,7 +9984,7 @@
       <c r="N236" s="17" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="22" t="n">
+      <c r="A237" s="13" t="n">
         <v>45980</v>
       </c>
       <c r="B237" s="14" t="inlineStr">
@@ -11325,7 +10034,7 @@
       <c r="N237" s="17" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="22" t="n">
+      <c r="A238" s="13" t="n">
         <v>45981</v>
       </c>
       <c r="B238" s="14" t="inlineStr">
@@ -11365,7 +10074,7 @@
       <c r="N238" s="17" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="22" t="n">
+      <c r="A239" s="13" t="n">
         <v>45982</v>
       </c>
       <c r="B239" s="14" t="inlineStr">
@@ -11375,7 +10084,7 @@
       </c>
       <c r="C239" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D239" s="15" t="inlineStr">
@@ -11385,7 +10094,7 @@
       </c>
       <c r="E239" s="15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F239" s="18" t="n">
@@ -11415,7 +10124,7 @@
       <c r="N239" s="17" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="22" t="n">
+      <c r="A240" s="13" t="n">
         <v>45985</v>
       </c>
       <c r="B240" s="14" t="inlineStr">
@@ -11455,7 +10164,7 @@
       <c r="N240" s="17" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="22" t="n">
+      <c r="A241" s="13" t="n">
         <v>45986</v>
       </c>
       <c r="B241" s="14" t="inlineStr">
@@ -11495,7 +10204,7 @@
       <c r="N241" s="17" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="22" t="n">
+      <c r="A242" s="13" t="n">
         <v>45987</v>
       </c>
       <c r="B242" s="14" t="inlineStr">
@@ -11545,7 +10254,7 @@
       <c r="N242" s="17" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="22" t="n">
+      <c r="A243" s="13" t="n">
         <v>45988</v>
       </c>
       <c r="B243" s="14" t="inlineStr">
@@ -11555,47 +10264,27 @@
       </c>
       <c r="C243" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D243" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E243" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F243" s="18" t="n">
-        <v>1.15882</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D243" s="15" t="n"/>
+      <c r="E243" s="15" t="n"/>
+      <c r="F243" s="14" t="n"/>
       <c r="G243" s="16" t="n"/>
       <c r="H243" s="17" t="n"/>
       <c r="I243" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J243" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K243" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L243" s="18" t="n">
-        <v>1.15763</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J243" s="15" t="n"/>
+      <c r="K243" s="15" t="n"/>
+      <c r="L243" s="14" t="n"/>
       <c r="M243" s="16" t="n"/>
       <c r="N243" s="17" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="22" t="n">
+      <c r="A244" s="13" t="n">
         <v>45989</v>
       </c>
       <c r="B244" s="14" t="inlineStr">
@@ -11605,22 +10294,12 @@
       </c>
       <c r="C244" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D244" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E244" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F244" s="18" t="n">
-        <v>1.158</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D244" s="15" t="n"/>
+      <c r="E244" s="15" t="n"/>
+      <c r="F244" s="14" t="n"/>
       <c r="G244" s="16" t="n"/>
       <c r="H244" s="17" t="n"/>
       <c r="I244" s="14" t="inlineStr">
@@ -11635,7 +10314,7 @@
       <c r="N244" s="17" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="22" t="n">
+      <c r="A245" s="13" t="n">
         <v>45992</v>
       </c>
       <c r="B245" s="14" t="inlineStr">
@@ -11645,22 +10324,12 @@
       </c>
       <c r="C245" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D245" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E245" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F245" s="18" t="n">
-        <v>1.16158</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D245" s="15" t="n"/>
+      <c r="E245" s="15" t="n"/>
+      <c r="F245" s="14" t="n"/>
       <c r="G245" s="16" t="n"/>
       <c r="H245" s="17" t="n"/>
       <c r="I245" s="14" t="inlineStr">
@@ -11685,7 +10354,7 @@
       <c r="N245" s="17" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="22" t="n">
+      <c r="A246" s="13" t="n">
         <v>45993</v>
       </c>
       <c r="B246" s="14" t="inlineStr">
@@ -11695,22 +10364,12 @@
       </c>
       <c r="C246" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D246" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E246" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F246" s="18" t="n">
-        <v>1.1614</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D246" s="15" t="n"/>
+      <c r="E246" s="15" t="n"/>
+      <c r="F246" s="14" t="n"/>
       <c r="G246" s="16" t="n"/>
       <c r="H246" s="17" t="n"/>
       <c r="I246" s="14" t="inlineStr">
@@ -11725,17 +10384,17 @@
       </c>
       <c r="K246" s="15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L246" s="18" t="n">
-        <v>1.16194</v>
+        <v>1.1623</v>
       </c>
       <c r="M246" s="16" t="n"/>
       <c r="N246" s="17" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="22" t="n">
+      <c r="A247" s="13" t="n">
         <v>45994</v>
       </c>
       <c r="B247" s="14" t="inlineStr">
@@ -11785,7 +10444,7 @@
       <c r="N247" s="17" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="22" t="n">
+      <c r="A248" s="13" t="n">
         <v>45995</v>
       </c>
       <c r="B248" s="14" t="inlineStr">
@@ -11835,7 +10494,7 @@
       <c r="N248" s="17" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="22" t="n">
+      <c r="A249" s="13" t="n">
         <v>45996</v>
       </c>
       <c r="B249" s="14" t="inlineStr">
@@ -11845,47 +10504,27 @@
       </c>
       <c r="C249" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D249" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E249" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F249" s="18" t="n">
-        <v>1.16543</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D249" s="15" t="n"/>
+      <c r="E249" s="15" t="n"/>
+      <c r="F249" s="14" t="n"/>
       <c r="G249" s="16" t="n"/>
       <c r="H249" s="17" t="n"/>
       <c r="I249" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J249" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K249" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L249" s="18" t="n">
-        <v>1.16717</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J249" s="15" t="n"/>
+      <c r="K249" s="15" t="n"/>
+      <c r="L249" s="14" t="n"/>
       <c r="M249" s="16" t="n"/>
       <c r="N249" s="17" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="22" t="n">
+      <c r="A250" s="13" t="n">
         <v>45999</v>
       </c>
       <c r="B250" s="14" t="inlineStr">
@@ -11895,7 +10534,7 @@
       </c>
       <c r="C250" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR2.2</t>
         </is>
       </c>
       <c r="D250" s="15" t="inlineStr">
@@ -11905,7 +10544,7 @@
       </c>
       <c r="E250" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="F250" s="18" t="n">
@@ -11915,27 +10554,17 @@
       <c r="H250" s="17" t="n"/>
       <c r="I250" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J250" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K250" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L250" s="18" t="n">
-        <v>1.16678</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J250" s="15" t="n"/>
+      <c r="K250" s="15" t="n"/>
+      <c r="L250" s="14" t="n"/>
       <c r="M250" s="16" t="n"/>
       <c r="N250" s="17" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="22" t="n">
+      <c r="A251" s="13" t="n">
         <v>46000</v>
       </c>
       <c r="B251" s="14" t="inlineStr">
@@ -11985,7 +10614,7 @@
       <c r="N251" s="17" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="22" t="n">
+      <c r="A252" s="13" t="n">
         <v>46001</v>
       </c>
       <c r="B252" s="14" t="inlineStr">
@@ -11995,47 +10624,27 @@
       </c>
       <c r="C252" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D252" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E252" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F252" s="18" t="n">
-        <v>1.16289</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D252" s="15" t="n"/>
+      <c r="E252" s="15" t="n"/>
+      <c r="F252" s="14" t="n"/>
       <c r="G252" s="16" t="n"/>
       <c r="H252" s="17" t="n"/>
       <c r="I252" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J252" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K252" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L252" s="18" t="n">
-        <v>1.16576</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J252" s="15" t="n"/>
+      <c r="K252" s="15" t="n"/>
+      <c r="L252" s="14" t="n"/>
       <c r="M252" s="16" t="n"/>
       <c r="N252" s="17" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="22" t="n">
+      <c r="A253" s="13" t="n">
         <v>46002</v>
       </c>
       <c r="B253" s="14" t="inlineStr">
@@ -12075,7 +10684,7 @@
       <c r="N253" s="17" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="22" t="n">
+      <c r="A254" s="13" t="n">
         <v>46003</v>
       </c>
       <c r="B254" s="14" t="inlineStr">
@@ -12085,47 +10694,27 @@
       </c>
       <c r="C254" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D254" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E254" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F254" s="18" t="n">
-        <v>1.1731</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D254" s="15" t="n"/>
+      <c r="E254" s="15" t="n"/>
+      <c r="F254" s="14" t="n"/>
       <c r="G254" s="16" t="n"/>
       <c r="H254" s="17" t="n"/>
       <c r="I254" s="14" t="inlineStr">
         <is>
-          <t>NYR1</t>
-        </is>
-      </c>
-      <c r="J254" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="K254" s="15" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="L254" s="18" t="n">
-        <v>1.17434</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J254" s="15" t="n"/>
+      <c r="K254" s="15" t="n"/>
+      <c r="L254" s="14" t="n"/>
       <c r="M254" s="16" t="n"/>
       <c r="N254" s="17" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="22" t="n">
+      <c r="A255" s="13" t="n">
         <v>46006</v>
       </c>
       <c r="B255" s="14" t="inlineStr">
@@ -12135,47 +10724,37 @@
       </c>
       <c r="C255" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D255" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E255" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F255" s="18" t="n">
-        <v>1.17277</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D255" s="15" t="n"/>
+      <c r="E255" s="15" t="n"/>
+      <c r="F255" s="14" t="n"/>
       <c r="G255" s="16" t="n"/>
       <c r="H255" s="17" t="n"/>
       <c r="I255" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J255" s="15" t="inlineStr">
         <is>
-          <t>largo</t>
+          <t>corto</t>
         </is>
       </c>
       <c r="K255" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L255" s="18" t="n">
-        <v>1.17264</v>
+        <v>1.17597</v>
       </c>
       <c r="M255" s="16" t="n"/>
       <c r="N255" s="17" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="22" t="n">
+      <c r="A256" s="13" t="n">
         <v>46007</v>
       </c>
       <c r="B256" s="14" t="inlineStr">
@@ -12185,21 +10764,21 @@
       </c>
       <c r="C256" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
+          <t>LR1</t>
         </is>
       </c>
       <c r="D256" s="15" t="inlineStr">
         <is>
-          <t>corto</t>
+          <t>largo</t>
         </is>
       </c>
       <c r="E256" s="15" t="inlineStr">
         <is>
-          <t>1er M15 04:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F256" s="18" t="n">
-        <v>1.1759</v>
+        <v>1.17467</v>
       </c>
       <c r="G256" s="16" t="n"/>
       <c r="H256" s="17" t="n"/>
@@ -12225,7 +10804,7 @@
       <c r="N256" s="17" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="22" t="n">
+      <c r="A257" s="13" t="n">
         <v>46008</v>
       </c>
       <c r="B257" s="14" t="inlineStr">
@@ -12235,47 +10814,27 @@
       </c>
       <c r="C257" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D257" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E257" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F257" s="18" t="n">
-        <v>1.17275</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D257" s="15" t="n"/>
+      <c r="E257" s="15" t="n"/>
+      <c r="F257" s="14" t="n"/>
       <c r="G257" s="16" t="n"/>
       <c r="H257" s="17" t="n"/>
       <c r="I257" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J257" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K257" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L257" s="18" t="n">
-        <v>1.1703</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J257" s="15" t="n"/>
+      <c r="K257" s="15" t="n"/>
+      <c r="L257" s="14" t="n"/>
       <c r="M257" s="16" t="n"/>
       <c r="N257" s="17" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="22" t="n">
+      <c r="A258" s="13" t="n">
         <v>46009</v>
       </c>
       <c r="B258" s="14" t="inlineStr">
@@ -12325,7 +10884,7 @@
       <c r="N258" s="17" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="22" t="n">
+      <c r="A259" s="13" t="n">
         <v>46010</v>
       </c>
       <c r="B259" s="14" t="inlineStr">
@@ -12335,27 +10894,17 @@
       </c>
       <c r="C259" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D259" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E259" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F259" s="18" t="n">
-        <v>1.17154</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D259" s="15" t="n"/>
+      <c r="E259" s="15" t="n"/>
+      <c r="F259" s="14" t="n"/>
       <c r="G259" s="16" t="n"/>
       <c r="H259" s="17" t="n"/>
       <c r="I259" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
+          <t>NYR1</t>
         </is>
       </c>
       <c r="J259" s="15" t="inlineStr">
@@ -12365,17 +10914,17 @@
       </c>
       <c r="K259" s="15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L259" s="18" t="n">
-        <v>1.17031</v>
+        <v>1.17021</v>
       </c>
       <c r="M259" s="16" t="n"/>
       <c r="N259" s="17" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="22" t="n">
+      <c r="A260" s="13" t="n">
         <v>46013</v>
       </c>
       <c r="B260" s="14" t="inlineStr">
@@ -12385,22 +10934,12 @@
       </c>
       <c r="C260" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D260" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E260" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F260" s="18" t="n">
-        <v>1.17216</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D260" s="15" t="n"/>
+      <c r="E260" s="15" t="n"/>
+      <c r="F260" s="14" t="n"/>
       <c r="G260" s="16" t="n"/>
       <c r="H260" s="17" t="n"/>
       <c r="I260" s="14" t="inlineStr">
@@ -12415,7 +10954,7 @@
       <c r="N260" s="17" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="22" t="n">
+      <c r="A261" s="13" t="n">
         <v>46014</v>
       </c>
       <c r="B261" s="14" t="inlineStr">
@@ -12425,47 +10964,27 @@
       </c>
       <c r="C261" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D261" s="15" t="inlineStr">
-        <is>
-          <t>corto</t>
-        </is>
-      </c>
-      <c r="E261" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F261" s="18" t="n">
-        <v>1.17803</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D261" s="15" t="n"/>
+      <c r="E261" s="15" t="n"/>
+      <c r="F261" s="14" t="n"/>
       <c r="G261" s="16" t="n"/>
       <c r="H261" s="17" t="n"/>
       <c r="I261" s="14" t="inlineStr">
         <is>
-          <t>NYR1</t>
-        </is>
-      </c>
-      <c r="J261" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K261" s="15" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="L261" s="18" t="n">
-        <v>1.17684</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J261" s="15" t="n"/>
+      <c r="K261" s="15" t="n"/>
+      <c r="L261" s="14" t="n"/>
       <c r="M261" s="16" t="n"/>
       <c r="N261" s="17" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="22" t="n">
+      <c r="A262" s="13" t="n">
         <v>46015</v>
       </c>
       <c r="B262" s="14" t="inlineStr">
@@ -12495,27 +11014,17 @@
       <c r="H262" s="17" t="n"/>
       <c r="I262" s="14" t="inlineStr">
         <is>
-          <t>NYC1</t>
-        </is>
-      </c>
-      <c r="J262" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="K262" s="15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="L262" s="18" t="n">
-        <v>1.17797</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J262" s="15" t="n"/>
+      <c r="K262" s="15" t="n"/>
+      <c r="L262" s="14" t="n"/>
       <c r="M262" s="16" t="n"/>
       <c r="N262" s="17" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="21" t="n">
+      <c r="A263" s="11" t="n">
         <v>46016</v>
       </c>
       <c r="B263" s="12" t="inlineStr">
@@ -12545,7 +11054,7 @@
       <c r="N263" s="12" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="22" t="n">
+      <c r="A264" s="13" t="n">
         <v>46017</v>
       </c>
       <c r="B264" s="14" t="inlineStr">
@@ -12555,22 +11064,12 @@
       </c>
       <c r="C264" s="14" t="inlineStr">
         <is>
-          <t>LR1</t>
-        </is>
-      </c>
-      <c r="D264" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E264" s="15" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F264" s="18" t="n">
-        <v>1.17755</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D264" s="15" t="n"/>
+      <c r="E264" s="15" t="n"/>
+      <c r="F264" s="14" t="n"/>
       <c r="G264" s="16" t="n"/>
       <c r="H264" s="17" t="n"/>
       <c r="I264" s="14" t="inlineStr">
@@ -12585,7 +11084,7 @@
       <c r="N264" s="17" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="22" t="n">
+      <c r="A265" s="13" t="n">
         <v>46020</v>
       </c>
       <c r="B265" s="14" t="inlineStr">
@@ -12625,7 +11124,7 @@
       <c r="N265" s="17" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="22" t="n">
+      <c r="A266" s="13" t="n">
         <v>46021</v>
       </c>
       <c r="B266" s="14" t="inlineStr">
@@ -12675,7 +11174,7 @@
       <c r="N266" s="17" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="22" t="n">
+      <c r="A267" s="13" t="n">
         <v>46022</v>
       </c>
       <c r="B267" s="14" t="inlineStr">
@@ -12685,22 +11184,12 @@
       </c>
       <c r="C267" s="14" t="inlineStr">
         <is>
-          <t>LR1*</t>
-        </is>
-      </c>
-      <c r="D267" s="15" t="inlineStr">
-        <is>
-          <t>largo</t>
-        </is>
-      </c>
-      <c r="E267" s="15" t="inlineStr">
-        <is>
-          <t>1er M15 04:00</t>
-        </is>
-      </c>
-      <c r="F267" s="18" t="n">
-        <v>1.1733</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D267" s="15" t="n"/>
+      <c r="E267" s="15" t="n"/>
+      <c r="F267" s="14" t="n"/>
       <c r="G267" s="16" t="n"/>
       <c r="H267" s="17" t="n"/>
       <c r="I267" s="14" t="inlineStr">
@@ -12714,7 +11203,6 @@
       <c r="M267" s="16" t="n"/>
       <c r="N267" s="17" t="n"/>
     </row>
-    <row r="268"/>
     <row r="269">
       <c r="A269" s="19" t="inlineStr">
         <is>
